--- a/public/madrid_cursos.xlsx
+++ b/public/madrid_cursos.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Buscador de Cursos - Público " sheetId="1" r:id="Rc28327f219d246b4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Buscador de Cursos - Público " sheetId="1" r:id="Rb021938f6cc84ec3"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -3171,24 +3171,21 @@
     <x:row r="94">
       <x:c r="A94" t="inlineStr">
         <x:is>
-          <x:t>25/5879</x:t>
+          <x:t>25/5364</x:t>
         </x:is>
       </x:c>
       <x:c r="B94" t="inlineStr">
         <x:is>
-          <x:t>SSCM0108</x:t>
+          <x:t>SSCE0109</x:t>
         </x:is>
       </x:c>
       <x:c r="C94" t="inlineStr">
         <x:is>
-          <x:t>LIMPIEZA DE SUPERFICIES Y MOBILIARIO EN EDIFICIOS Y LOCALES</x:t>
+          <x:t>INFORMACIÓN JUVENIL</x:t>
         </x:is>
       </x:c>
       <x:c r="D94" s="1" t="n">
-        <x:v>46146.9166666667</x:v>
-      </x:c>
-      <x:c r="E94" s="2" t="n">
-        <x:v>46205.9166666667</x:v>
+        <x:v>46145.9166666667</x:v>
       </x:c>
       <x:c r="F94" t="inlineStr">
         <x:is>
@@ -3197,14 +3194,14 @@
       </x:c>
       <x:c r="G94" t="inlineStr">
         <x:is>
-          <x:t>CRUZ ROJA ESPAÑOLA</x:t>
+          <x:t>SERPROFES SL</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="95">
       <x:c r="A95" t="inlineStr">
         <x:is>
-          <x:t>25/5364</x:t>
+          <x:t>25/5411</x:t>
         </x:is>
       </x:c>
       <x:c r="B95" t="inlineStr">
@@ -3220,6 +3217,9 @@
       <x:c r="D95" s="1" t="n">
         <x:v>46145.9166666667</x:v>
       </x:c>
+      <x:c r="E95" s="2" t="n">
+        <x:v>46233.9166666667</x:v>
+      </x:c>
       <x:c r="F95" t="inlineStr">
         <x:is>
           <x:t>Presencial</x:t>
@@ -3227,90 +3227,90 @@
       </x:c>
       <x:c r="G95" t="inlineStr">
         <x:is>
-          <x:t>SERPROFES SL</x:t>
+          <x:t>INNOVACION Y DESARROLLO LOCAL, S.L.</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="96">
       <x:c r="A96" t="inlineStr">
         <x:is>
-          <x:t>25/5411</x:t>
+          <x:t>25/5475</x:t>
         </x:is>
       </x:c>
       <x:c r="B96" t="inlineStr">
         <x:is>
-          <x:t>SSCE0109</x:t>
+          <x:t>SSCS0108</x:t>
         </x:is>
       </x:c>
       <x:c r="C96" t="inlineStr">
         <x:is>
-          <x:t>INFORMACIÓN JUVENIL</x:t>
+          <x:t>ATENCIÓN SOCIOSANITARIA A PERSONAS EN EL DOMICILIO</x:t>
         </x:is>
       </x:c>
       <x:c r="D96" s="1" t="n">
         <x:v>46145.9166666667</x:v>
       </x:c>
       <x:c r="E96" s="2" t="n">
-        <x:v>46233.9166666667</x:v>
+        <x:v>46271.9166666667</x:v>
       </x:c>
       <x:c r="F96" t="inlineStr">
         <x:is>
-          <x:t>Presencial</x:t>
+          <x:t>Teleformación</x:t>
         </x:is>
       </x:c>
       <x:c r="G96" t="inlineStr">
         <x:is>
-          <x:t>INNOVACION Y DESARROLLO LOCAL, S.L.</x:t>
+          <x:t>AUTOESCUELA GALA S.L.</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="97">
       <x:c r="A97" t="inlineStr">
         <x:is>
-          <x:t>25/5475</x:t>
+          <x:t>25/8069</x:t>
         </x:is>
       </x:c>
       <x:c r="B97" t="inlineStr">
         <x:is>
-          <x:t>SSCS0108</x:t>
+          <x:t>SSCE0110</x:t>
         </x:is>
       </x:c>
       <x:c r="C97" t="inlineStr">
         <x:is>
-          <x:t>ATENCIÓN SOCIOSANITARIA A PERSONAS EN EL DOMICILIO</x:t>
+          <x:t>HABILITACIÓN PARA LA DOCENCIA EN GRADOS A, B Y C DEL SISTEMA DE FORMACIÓN PROFESIONAL</x:t>
         </x:is>
       </x:c>
       <x:c r="D97" s="1" t="n">
         <x:v>46145.9166666667</x:v>
       </x:c>
       <x:c r="E97" s="2" t="n">
-        <x:v>46271.9166666667</x:v>
+        <x:v>46211.9166666667</x:v>
       </x:c>
       <x:c r="F97" t="inlineStr">
         <x:is>
-          <x:t>Teleformación</x:t>
+          <x:t>Presencial</x:t>
         </x:is>
       </x:c>
       <x:c r="G97" t="inlineStr">
         <x:is>
-          <x:t>AUTOESCUELA GALA S.L.</x:t>
+          <x:t>MOSTOLES DESARROLLO PROMOCION ECONOMICA S.A.</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="98">
       <x:c r="A98" t="inlineStr">
         <x:is>
-          <x:t>25/8069</x:t>
+          <x:t>25/8083</x:t>
         </x:is>
       </x:c>
       <x:c r="B98" t="inlineStr">
         <x:is>
-          <x:t>SSCE0110</x:t>
+          <x:t>COML0309</x:t>
         </x:is>
       </x:c>
       <x:c r="C98" t="inlineStr">
         <x:is>
-          <x:t>HABILITACIÓN PARA LA DOCENCIA EN GRADOS A, B Y C DEL SISTEMA DE FORMACIÓN PROFESIONAL</x:t>
+          <x:t>ORGANIZACIÓN Y GESTIÓN DE ALMACENES</x:t>
         </x:is>
       </x:c>
       <x:c r="D98" s="1" t="n">
@@ -3326,31 +3326,26 @@
       </x:c>
       <x:c r="G98" t="inlineStr">
         <x:is>
-          <x:t>MOSTOLES DESARROLLO PROMOCION ECONOMICA S.A.</x:t>
+          <x:t>ENTE PUBLICO EMPRESARIAL ALCALA DESARROLLO</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="99">
       <x:c r="A99" t="inlineStr">
         <x:is>
-          <x:t>25/8083</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B99" t="inlineStr">
-        <x:is>
-          <x:t>COML0309</x:t>
+          <x:t>25/2319</x:t>
         </x:is>
       </x:c>
       <x:c r="C99" t="inlineStr">
         <x:is>
-          <x:t>ORGANIZACIÓN Y GESTIÓN DE ALMACENES</x:t>
+          <x:t>OFIMÁTICA</x:t>
         </x:is>
       </x:c>
       <x:c r="D99" s="1" t="n">
-        <x:v>46145.9166666667</x:v>
+        <x:v>46141.9166666667</x:v>
       </x:c>
       <x:c r="E99" s="2" t="n">
-        <x:v>46211.9166666667</x:v>
+        <x:v>46196.9166666667</x:v>
       </x:c>
       <x:c r="F99" t="inlineStr">
         <x:is>
@@ -3359,26 +3354,36 @@
       </x:c>
       <x:c r="G99" t="inlineStr">
         <x:is>
-          <x:t>ENTE PUBLICO EMPRESARIAL ALCALA DESARROLLO</x:t>
+          <x:t>CENTRO DE FORMACIÓN DIGITAL SAN BLAS</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H99" t="inlineStr">
+        <x:is>
+          <x:t>MADRID</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="100">
       <x:c r="A100" t="inlineStr">
         <x:is>
-          <x:t>25/2319</x:t>
+          <x:t>23/8007</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B100" t="inlineStr">
+        <x:is>
+          <x:t>AFDA0110</x:t>
         </x:is>
       </x:c>
       <x:c r="C100" t="inlineStr">
         <x:is>
-          <x:t>OFIMÁTICA</x:t>
+          <x:t>ACONDICIONAMIENTO FÍSICO EN GRUPO CON SOPORTE MUSICAL</x:t>
         </x:is>
       </x:c>
       <x:c r="D100" s="1" t="n">
-        <x:v>46141.9166666667</x:v>
+        <x:v>46139.9166666667</x:v>
       </x:c>
       <x:c r="E100" s="2" t="n">
-        <x:v>46196.9166666667</x:v>
+        <x:v>46293.9166666667</x:v>
       </x:c>
       <x:c r="F100" t="inlineStr">
         <x:is>
@@ -3387,36 +3392,31 @@
       </x:c>
       <x:c r="G100" t="inlineStr">
         <x:is>
-          <x:t>CENTRO DE FORMACIÓN DIGITAL SAN BLAS</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H100" t="inlineStr">
-        <x:is>
-          <x:t>MADRID</x:t>
+          <x:t>ANGEL FERNANDEZ-ROLDAN GONZALEZ</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="101">
       <x:c r="A101" t="inlineStr">
         <x:is>
-          <x:t>23/8007</x:t>
+          <x:t>23/8351</x:t>
         </x:is>
       </x:c>
       <x:c r="B101" t="inlineStr">
         <x:is>
-          <x:t>AFDA0110</x:t>
+          <x:t>COMP0108</x:t>
         </x:is>
       </x:c>
       <x:c r="C101" t="inlineStr">
         <x:is>
-          <x:t>ACONDICIONAMIENTO FÍSICO EN GRUPO CON SOPORTE MUSICAL</x:t>
+          <x:t>IMPLANTACIÓN Y ANIMACIÓN DE ESPACIOS COMERCIALES</x:t>
         </x:is>
       </x:c>
       <x:c r="D101" s="1" t="n">
         <x:v>46139.9166666667</x:v>
       </x:c>
       <x:c r="E101" s="2" t="n">
-        <x:v>46293.9166666667</x:v>
+        <x:v>46288.9166666667</x:v>
       </x:c>
       <x:c r="F101" t="inlineStr">
         <x:is>
@@ -3425,31 +3425,31 @@
       </x:c>
       <x:c r="G101" t="inlineStr">
         <x:is>
-          <x:t>ANGEL FERNANDEZ-ROLDAN GONZALEZ</x:t>
+          <x:t>KNOWLEDGE INNOVATION WORKS, S.L.</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="102">
       <x:c r="A102" t="inlineStr">
         <x:is>
-          <x:t>23/8351</x:t>
+          <x:t>25/5474</x:t>
         </x:is>
       </x:c>
       <x:c r="B102" t="inlineStr">
         <x:is>
-          <x:t>COMP0108</x:t>
+          <x:t>SSCS0108</x:t>
         </x:is>
       </x:c>
       <x:c r="C102" t="inlineStr">
         <x:is>
-          <x:t>IMPLANTACIÓN Y ANIMACIÓN DE ESPACIOS COMERCIALES</x:t>
+          <x:t>ATENCIÓN SOCIOSANITARIA A PERSONAS EN EL DOMICILIO</x:t>
         </x:is>
       </x:c>
       <x:c r="D102" s="1" t="n">
-        <x:v>46139.9166666667</x:v>
+        <x:v>46138.9166666667</x:v>
       </x:c>
       <x:c r="E102" s="2" t="n">
-        <x:v>46288.9166666667</x:v>
+        <x:v>46308.9166666667</x:v>
       </x:c>
       <x:c r="F102" t="inlineStr">
         <x:is>
@@ -3458,31 +3458,31 @@
       </x:c>
       <x:c r="G102" t="inlineStr">
         <x:is>
-          <x:t>KNOWLEDGE INNOVATION WORKS, S.L.</x:t>
+          <x:t>AUTOESCUELA GALA S.L.</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="103">
       <x:c r="A103" t="inlineStr">
         <x:is>
-          <x:t>25/5474</x:t>
+          <x:t>25/5554</x:t>
         </x:is>
       </x:c>
       <x:c r="B103" t="inlineStr">
         <x:is>
-          <x:t>SSCS0108</x:t>
+          <x:t>EOCJ0211</x:t>
         </x:is>
       </x:c>
       <x:c r="C103" t="inlineStr">
         <x:is>
-          <x:t>ATENCIÓN SOCIOSANITARIA A PERSONAS EN EL DOMICILIO</x:t>
+          <x:t>INSTALACIÓN DE SISTEMAS TÉCNICOS DE PAVIMENTOS, EMPANELADOS Y MAMPARAS</x:t>
         </x:is>
       </x:c>
       <x:c r="D103" s="1" t="n">
-        <x:v>46138.9166666667</x:v>
+        <x:v>46134.9166666667</x:v>
       </x:c>
       <x:c r="E103" s="2" t="n">
-        <x:v>46308.9166666667</x:v>
+        <x:v>46201.9166666667</x:v>
       </x:c>
       <x:c r="F103" t="inlineStr">
         <x:is>
@@ -3491,97 +3491,92 @@
       </x:c>
       <x:c r="G103" t="inlineStr">
         <x:is>
-          <x:t>AUTOESCUELA GALA S.L.</x:t>
+          <x:t>ADARA FORMACION, S.L.</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="104">
       <x:c r="A104" t="inlineStr">
         <x:is>
-          <x:t>25/5554</x:t>
+          <x:t>25/5587</x:t>
         </x:is>
       </x:c>
       <x:c r="B104" t="inlineStr">
         <x:is>
-          <x:t>EOCJ0211</x:t>
+          <x:t>COMV0108</x:t>
         </x:is>
       </x:c>
       <x:c r="C104" t="inlineStr">
         <x:is>
-          <x:t>INSTALACIÓN DE SISTEMAS TÉCNICOS DE PAVIMENTOS, EMPANELADOS Y MAMPARAS</x:t>
+          <x:t>ACTIVIDADES DE VENTA</x:t>
         </x:is>
       </x:c>
       <x:c r="D104" s="1" t="n">
         <x:v>46134.9166666667</x:v>
       </x:c>
       <x:c r="E104" s="2" t="n">
-        <x:v>46201.9166666667</x:v>
+        <x:v>46338.9583333333</x:v>
       </x:c>
       <x:c r="F104" t="inlineStr">
         <x:is>
-          <x:t>Presencial</x:t>
+          <x:t>Teleformación</x:t>
         </x:is>
       </x:c>
       <x:c r="G104" t="inlineStr">
         <x:is>
-          <x:t>ADARA FORMACION, S.L.</x:t>
+          <x:t>KNOWLEDGE INNOVATION WORKS, S.L.</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="105">
       <x:c r="A105" t="inlineStr">
         <x:is>
-          <x:t>25/5587</x:t>
+          <x:t>25/8076</x:t>
         </x:is>
       </x:c>
       <x:c r="B105" t="inlineStr">
         <x:is>
-          <x:t>COMV0108</x:t>
+          <x:t>SSCS0208</x:t>
         </x:is>
       </x:c>
       <x:c r="C105" t="inlineStr">
         <x:is>
-          <x:t>ACTIVIDADES DE VENTA</x:t>
+          <x:t>ATENCIÓN SOCIOSANITARIA A PERSONAS DEPENDIENTES EN INSTITUCIONES SOCIALES</x:t>
         </x:is>
       </x:c>
       <x:c r="D105" s="1" t="n">
         <x:v>46134.9166666667</x:v>
       </x:c>
       <x:c r="E105" s="2" t="n">
-        <x:v>46338.9583333333</x:v>
+        <x:v>46224.9166666667</x:v>
       </x:c>
       <x:c r="F105" t="inlineStr">
         <x:is>
-          <x:t>Teleformación</x:t>
+          <x:t>Presencial</x:t>
         </x:is>
       </x:c>
       <x:c r="G105" t="inlineStr">
         <x:is>
-          <x:t>KNOWLEDGE INNOVATION WORKS, S.L.</x:t>
+          <x:t>MOSTOLES DESARROLLO PROMOCION ECONOMICA S.A.</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="106">
       <x:c r="A106" t="inlineStr">
         <x:is>
-          <x:t>25/8076</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B106" t="inlineStr">
-        <x:is>
-          <x:t>SSCS0208</x:t>
+          <x:t>25/2415</x:t>
         </x:is>
       </x:c>
       <x:c r="C106" t="inlineStr">
         <x:is>
-          <x:t>ATENCIÓN SOCIOSANITARIA A PERSONAS DEPENDIENTES EN INSTITUCIONES SOCIALES</x:t>
+          <x:t>SEGURIDAD INFORMÁTICA</x:t>
         </x:is>
       </x:c>
       <x:c r="D106" s="1" t="n">
         <x:v>46134.9166666667</x:v>
       </x:c>
       <x:c r="E106" s="2" t="n">
-        <x:v>46224.9166666667</x:v>
+        <x:v>46271.9166666667</x:v>
       </x:c>
       <x:c r="F106" t="inlineStr">
         <x:is>
@@ -3590,26 +3585,36 @@
       </x:c>
       <x:c r="G106" t="inlineStr">
         <x:is>
-          <x:t>MOSTOLES DESARROLLO PROMOCION ECONOMICA S.A.</x:t>
+          <x:t>CENTRO DE FORMACIÓN DIGITAL SAN BLAS</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H106" t="inlineStr">
+        <x:is>
+          <x:t>MADRID</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="107">
       <x:c r="A107" t="inlineStr">
         <x:is>
-          <x:t>25/2415</x:t>
+          <x:t>25/5658</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B107" t="inlineStr">
+        <x:is>
+          <x:t>TCPF0309</x:t>
         </x:is>
       </x:c>
       <x:c r="C107" t="inlineStr">
         <x:is>
-          <x:t>SEGURIDAD INFORMÁTICA</x:t>
+          <x:t>CORTINAJE Y COMPLEMENTOS DE DECORACIÓN</x:t>
         </x:is>
       </x:c>
       <x:c r="D107" s="1" t="n">
-        <x:v>46134.9166666667</x:v>
+        <x:v>46133.9166666667</x:v>
       </x:c>
       <x:c r="E107" s="2" t="n">
-        <x:v>46271.9166666667</x:v>
+        <x:v>46215.9166666667</x:v>
       </x:c>
       <x:c r="F107" t="inlineStr">
         <x:is>
@@ -3618,36 +3623,31 @@
       </x:c>
       <x:c r="G107" t="inlineStr">
         <x:is>
-          <x:t>CENTRO DE FORMACIÓN DIGITAL SAN BLAS</x:t>
+          <x:t>FORMACION INTERNACIONAL VOCACIONAL Y EMPRENDIMIENTO, S.L.</x:t>
         </x:is>
       </x:c>
       <x:c r="H107" t="inlineStr">
         <x:is>
-          <x:t>MADRID</x:t>
+          <x:t>Alcala de Henares</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="108">
       <x:c r="A108" t="inlineStr">
         <x:is>
-          <x:t>25/5658</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B108" t="inlineStr">
-        <x:is>
-          <x:t>TCPF0309</x:t>
+          <x:t>25/9010</x:t>
         </x:is>
       </x:c>
       <x:c r="C108" t="inlineStr">
         <x:is>
-          <x:t>CORTINAJE Y COMPLEMENTOS DE DECORACIÓN</x:t>
+          <x:t>ACTIVIDADES ADMINISTRATIVAS EN LA RELACIÓN CON EL CLIENTE</x:t>
         </x:is>
       </x:c>
       <x:c r="D108" s="1" t="n">
         <x:v>46133.9166666667</x:v>
       </x:c>
       <x:c r="E108" s="2" t="n">
-        <x:v>46215.9166666667</x:v>
+        <x:v>46335.9583333333</x:v>
       </x:c>
       <x:c r="F108" t="inlineStr">
         <x:is>
@@ -3656,31 +3656,36 @@
       </x:c>
       <x:c r="G108" t="inlineStr">
         <x:is>
-          <x:t>FORMACION INTERNACIONAL VOCACIONAL Y EMPRENDIMIENTO, S.L.</x:t>
+          <x:t>FIVE ALCALA</x:t>
         </x:is>
       </x:c>
       <x:c r="H108" t="inlineStr">
         <x:is>
-          <x:t>Alcala de Henares</x:t>
+          <x:t>ALCALA DE HENARES</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="109">
       <x:c r="A109" t="inlineStr">
         <x:is>
-          <x:t>25/9010</x:t>
+          <x:t>25/5113</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B109" t="inlineStr">
+        <x:is>
+          <x:t>SEA_C_001_4B</x:t>
         </x:is>
       </x:c>
       <x:c r="C109" t="inlineStr">
         <x:is>
-          <x:t>ACTIVIDADES ADMINISTRATIVAS EN LA RELACIÓN CON EL CLIENTE</x:t>
+          <x:t>SERVICIOS DE CONTROL DE PLAGAS/ORGANISMOS NOCIVOS.</x:t>
         </x:is>
       </x:c>
       <x:c r="D109" s="1" t="n">
-        <x:v>46133.9166666667</x:v>
+        <x:v>46132.9166666667</x:v>
       </x:c>
       <x:c r="E109" s="2" t="n">
-        <x:v>46335.9583333333</x:v>
+        <x:v>46222.9166666667</x:v>
       </x:c>
       <x:c r="F109" t="inlineStr">
         <x:is>
@@ -3689,36 +3694,31 @@
       </x:c>
       <x:c r="G109" t="inlineStr">
         <x:is>
-          <x:t>FIVE ALCALA</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H109" t="inlineStr">
-        <x:is>
-          <x:t>ALCALA DE HENARES</x:t>
+          <x:t>COLEGIO SAN ISIDRO, S.L.</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="110">
       <x:c r="A110" t="inlineStr">
         <x:is>
-          <x:t>25/5113</x:t>
+          <x:t>23/8417</x:t>
         </x:is>
       </x:c>
       <x:c r="B110" t="inlineStr">
         <x:is>
-          <x:t>SEA_C_001_4B</x:t>
+          <x:t>MAMD0209</x:t>
         </x:is>
       </x:c>
       <x:c r="C110" t="inlineStr">
         <x:is>
-          <x:t>SERVICIOS DE CONTROL DE PLAGAS/ORGANISMOS NOCIVOS.</x:t>
+          <x:t>TRABAJOS DE CARPINTERÍA Y MUEBLE</x:t>
         </x:is>
       </x:c>
       <x:c r="D110" s="1" t="n">
-        <x:v>46132.9166666667</x:v>
+        <x:v>46131.9166666667</x:v>
       </x:c>
       <x:c r="E110" s="2" t="n">
-        <x:v>46222.9166666667</x:v>
+        <x:v>46194.9166666667</x:v>
       </x:c>
       <x:c r="F110" t="inlineStr">
         <x:is>
@@ -3727,31 +3727,31 @@
       </x:c>
       <x:c r="G110" t="inlineStr">
         <x:is>
-          <x:t>COLEGIO SAN ISIDRO, S.L.</x:t>
+          <x:t>FUNDACION CARMEN PARDO-VALCARCE</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H110" t="inlineStr">
+        <x:is>
+          <x:t>Madrid</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="111">
       <x:c r="A111" t="inlineStr">
         <x:is>
-          <x:t>23/8417</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B111" t="inlineStr">
-        <x:is>
-          <x:t>MAMD0209</x:t>
+          <x:t>25/5657</x:t>
         </x:is>
       </x:c>
       <x:c r="C111" t="inlineStr">
         <x:is>
-          <x:t>TRABAJOS DE CARPINTERÍA Y MUEBLE</x:t>
+          <x:t>CONFECCIÓN DE VESTUARIO A MEDIDA EN TEXTIL Y PIEL</x:t>
         </x:is>
       </x:c>
       <x:c r="D111" s="1" t="n">
         <x:v>46131.9166666667</x:v>
       </x:c>
       <x:c r="E111" s="2" t="n">
-        <x:v>46194.9166666667</x:v>
+        <x:v>46299.9166666667</x:v>
       </x:c>
       <x:c r="F111" t="inlineStr">
         <x:is>
@@ -3760,31 +3760,36 @@
       </x:c>
       <x:c r="G111" t="inlineStr">
         <x:is>
-          <x:t>FUNDACION CARMEN PARDO-VALCARCE</x:t>
+          <x:t>FORMACION INTERNACIONAL VOCACIONAL Y EMPRENDIMIENTO, S.L.</x:t>
         </x:is>
       </x:c>
       <x:c r="H111" t="inlineStr">
         <x:is>
-          <x:t>Madrid</x:t>
+          <x:t>Alcala de Henares</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="112">
       <x:c r="A112" t="inlineStr">
         <x:is>
-          <x:t>25/5657</x:t>
+          <x:t>25/5421</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B112" t="inlineStr">
+        <x:is>
+          <x:t>HOTR0209</x:t>
         </x:is>
       </x:c>
       <x:c r="C112" t="inlineStr">
         <x:is>
-          <x:t>CONFECCIÓN DE VESTUARIO A MEDIDA EN TEXTIL Y PIEL</x:t>
+          <x:t>SUMILLERÍA</x:t>
         </x:is>
       </x:c>
       <x:c r="D112" s="1" t="n">
-        <x:v>46131.9166666667</x:v>
+        <x:v>46127.9166666667</x:v>
       </x:c>
       <x:c r="E112" s="2" t="n">
-        <x:v>46299.9166666667</x:v>
+        <x:v>46204.9166666667</x:v>
       </x:c>
       <x:c r="F112" t="inlineStr">
         <x:is>
@@ -3793,112 +3798,107 @@
       </x:c>
       <x:c r="G112" t="inlineStr">
         <x:is>
-          <x:t>FORMACION INTERNACIONAL VOCACIONAL Y EMPRENDIMIENTO, S.L.</x:t>
+          <x:t>TALLER CEFORA S.L.</x:t>
         </x:is>
       </x:c>
       <x:c r="H112" t="inlineStr">
         <x:is>
-          <x:t>Alcala de Henares</x:t>
+          <x:t>Móstoles</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="113">
       <x:c r="A113" t="inlineStr">
         <x:is>
-          <x:t>25/5421</x:t>
+          <x:t>25/5562</x:t>
         </x:is>
       </x:c>
       <x:c r="B113" t="inlineStr">
         <x:is>
-          <x:t>HOTR0209</x:t>
+          <x:t>IMPP0208</x:t>
         </x:is>
       </x:c>
       <x:c r="C113" t="inlineStr">
         <x:is>
-          <x:t>SUMILLERÍA</x:t>
+          <x:t>SERVICIOS ESTÉTICOS DE HIGIENE, DEPILACIÓN Y MAQUILLAJE</x:t>
         </x:is>
       </x:c>
       <x:c r="D113" s="1" t="n">
         <x:v>46127.9166666667</x:v>
       </x:c>
       <x:c r="E113" s="2" t="n">
-        <x:v>46204.9166666667</x:v>
+        <x:v>46278.9166666667</x:v>
       </x:c>
       <x:c r="F113" t="inlineStr">
         <x:is>
-          <x:t>Presencial</x:t>
+          <x:t>Teleformación</x:t>
         </x:is>
       </x:c>
       <x:c r="G113" t="inlineStr">
         <x:is>
-          <x:t>TALLER CEFORA S.L.</x:t>
+          <x:t>CENTRO ARANDA SCHOLA SL</x:t>
         </x:is>
       </x:c>
       <x:c r="H113" t="inlineStr">
         <x:is>
-          <x:t>Móstoles</x:t>
+          <x:t>MADRID</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="114">
       <x:c r="A114" t="inlineStr">
         <x:is>
-          <x:t>25/5562</x:t>
+          <x:t>25/8077</x:t>
         </x:is>
       </x:c>
       <x:c r="B114" t="inlineStr">
         <x:is>
-          <x:t>IMPP0208</x:t>
+          <x:t>ADGG0408</x:t>
         </x:is>
       </x:c>
       <x:c r="C114" t="inlineStr">
         <x:is>
-          <x:t>SERVICIOS ESTÉTICOS DE HIGIENE, DEPILACIÓN Y MAQUILLAJE</x:t>
+          <x:t>OPERACIONES AUXILIARES DE SERVICIOS ADMINISTRATIVOS Y GENERALES</x:t>
         </x:is>
       </x:c>
       <x:c r="D114" s="1" t="n">
         <x:v>46127.9166666667</x:v>
       </x:c>
       <x:c r="E114" s="2" t="n">
-        <x:v>46278.9166666667</x:v>
+        <x:v>46209.9166666667</x:v>
       </x:c>
       <x:c r="F114" t="inlineStr">
         <x:is>
-          <x:t>Teleformación</x:t>
+          <x:t>Presencial</x:t>
         </x:is>
       </x:c>
       <x:c r="G114" t="inlineStr">
         <x:is>
-          <x:t>CENTRO ARANDA SCHOLA SL</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H114" t="inlineStr">
-        <x:is>
-          <x:t>MADRID</x:t>
+          <x:t>ENTE PUBLICO EMPRESARIAL ALCALA DESARROLLO</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="115">
       <x:c r="A115" t="inlineStr">
         <x:is>
-          <x:t>25/8077</x:t>
+          <x:t>25/5705</x:t>
         </x:is>
       </x:c>
       <x:c r="B115" t="inlineStr">
         <x:is>
-          <x:t>ADGG0408</x:t>
+          <x:t>SSCG0112</x:t>
         </x:is>
       </x:c>
       <x:c r="C115" t="inlineStr">
         <x:is>
-          <x:t>OPERACIONES AUXILIARES DE SERVICIOS ADMINISTRATIVOS Y GENERALES</x:t>
+          <x:t>PROMOCIÓN Y PARTICIPACIÓN DE LA COMUNIDAD SORDA</x:t>
         </x:is>
       </x:c>
       <x:c r="D115" s="1" t="n">
-        <x:v>46127.9166666667</x:v>
+        <x:v>46126.9583333333</x:v>
       </x:c>
       <x:c r="E115" s="2" t="n">
-        <x:v>46209.9166666667</x:v>
+        <x:v>46337.9583333333</x:v>
       </x:c>
       <x:c r="F115" t="inlineStr">
         <x:is>
@@ -3907,14 +3907,14 @@
       </x:c>
       <x:c r="G115" t="inlineStr">
         <x:is>
-          <x:t>ENTE PUBLICO EMPRESARIAL ALCALA DESARROLLO</x:t>
+          <x:t>FORMACION PARA EL DESARROLLO E INSERCION SL</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="116">
       <x:c r="A116" t="inlineStr">
         <x:is>
-          <x:t>25/5705</x:t>
+          <x:t>25/5706</x:t>
         </x:is>
       </x:c>
       <x:c r="B116" t="inlineStr">
@@ -3947,24 +3947,24 @@
     <x:row r="117">
       <x:c r="A117" t="inlineStr">
         <x:is>
-          <x:t>25/5706</x:t>
+          <x:t>23/8352</x:t>
         </x:is>
       </x:c>
       <x:c r="B117" t="inlineStr">
         <x:is>
-          <x:t>SSCG0112</x:t>
+          <x:t>IFCT0108</x:t>
         </x:is>
       </x:c>
       <x:c r="C117" t="inlineStr">
         <x:is>
-          <x:t>PROMOCIÓN Y PARTICIPACIÓN DE LA COMUNIDAD SORDA</x:t>
+          <x:t>OPERACIONES AUXILIARES DE MONTAJE Y MANTENIMIENTO DE SISTEMAS MICROINFORMÁTICOS</x:t>
         </x:is>
       </x:c>
       <x:c r="D117" s="1" t="n">
-        <x:v>46126.9583333333</x:v>
+        <x:v>46126.9166666667</x:v>
       </x:c>
       <x:c r="E117" s="2" t="n">
-        <x:v>46337.9583333333</x:v>
+        <x:v>46215.9166666667</x:v>
       </x:c>
       <x:c r="F117" t="inlineStr">
         <x:is>
@@ -3973,31 +3973,31 @@
       </x:c>
       <x:c r="G117" t="inlineStr">
         <x:is>
-          <x:t>FORMACION PARA EL DESARROLLO E INSERCION SL</x:t>
+          <x:t>KNOWLEDGE INNOVATION WORKS, S.L.</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="118">
       <x:c r="A118" t="inlineStr">
         <x:is>
-          <x:t>23/8352</x:t>
+          <x:t>25/5704</x:t>
         </x:is>
       </x:c>
       <x:c r="B118" t="inlineStr">
         <x:is>
-          <x:t>IFCT0108</x:t>
+          <x:t>COMT0411</x:t>
         </x:is>
       </x:c>
       <x:c r="C118" t="inlineStr">
         <x:is>
-          <x:t>OPERACIONES AUXILIARES DE MONTAJE Y MANTENIMIENTO DE SISTEMAS MICROINFORMÁTICOS</x:t>
+          <x:t>GESTIÓN COMERCIAL DE VENTAS</x:t>
         </x:is>
       </x:c>
       <x:c r="D118" s="1" t="n">
-        <x:v>46126.9166666667</x:v>
+        <x:v>46125.9583333333</x:v>
       </x:c>
       <x:c r="E118" s="2" t="n">
-        <x:v>46215.9166666667</x:v>
+        <x:v>46279.9583333333</x:v>
       </x:c>
       <x:c r="F118" t="inlineStr">
         <x:is>
@@ -4006,31 +4006,26 @@
       </x:c>
       <x:c r="G118" t="inlineStr">
         <x:is>
-          <x:t>KNOWLEDGE INNOVATION WORKS, S.L.</x:t>
+          <x:t>FORMACION PARA EL DESARROLLO E INSERCION SL</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="119">
       <x:c r="A119" t="inlineStr">
         <x:is>
-          <x:t>25/5704</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B119" t="inlineStr">
-        <x:is>
-          <x:t>COMT0411</x:t>
+          <x:t>25/9531</x:t>
         </x:is>
       </x:c>
       <x:c r="C119" t="inlineStr">
         <x:is>
-          <x:t>GESTIÓN COMERCIAL DE VENTAS</x:t>
+          <x:t>ATENCIÓN SOCIOSANITARIA A PERSONAS DEPENDIENTES EN INSTITUCIONES SOCIALES</x:t>
         </x:is>
       </x:c>
       <x:c r="D119" s="1" t="n">
-        <x:v>46125.9583333333</x:v>
+        <x:v>46125.9166666667</x:v>
       </x:c>
       <x:c r="E119" s="2" t="n">
-        <x:v>46279.9583333333</x:v>
+        <x:v>46302.9166666667</x:v>
       </x:c>
       <x:c r="F119" t="inlineStr">
         <x:is>
@@ -4039,26 +4034,36 @@
       </x:c>
       <x:c r="G119" t="inlineStr">
         <x:is>
-          <x:t>FORMACION PARA EL DESARROLLO E INSERCION SL</x:t>
+          <x:t>DETUATUFORMACION S.L.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H119" t="inlineStr">
+        <x:is>
+          <x:t>MADRID</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="120">
       <x:c r="A120" t="inlineStr">
         <x:is>
-          <x:t>25/9531</x:t>
+          <x:t>25/5143</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B120" t="inlineStr">
+        <x:is>
+          <x:t>SSCE0110</x:t>
         </x:is>
       </x:c>
       <x:c r="C120" t="inlineStr">
         <x:is>
-          <x:t>ATENCIÓN SOCIOSANITARIA A PERSONAS DEPENDIENTES EN INSTITUCIONES SOCIALES</x:t>
+          <x:t>HABILITACIÓN PARA LA DOCENCIA EN GRADOS A, B Y C DEL SISTEMA DE FORMACIÓN PROFESIONAL</x:t>
         </x:is>
       </x:c>
       <x:c r="D120" s="1" t="n">
         <x:v>46125.9166666667</x:v>
       </x:c>
       <x:c r="E120" s="2" t="n">
-        <x:v>46302.9166666667</x:v>
+        <x:v>46198.9166666667</x:v>
       </x:c>
       <x:c r="F120" t="inlineStr">
         <x:is>
@@ -4067,36 +4072,31 @@
       </x:c>
       <x:c r="G120" t="inlineStr">
         <x:is>
-          <x:t>DETUATUFORMACION S.L.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H120" t="inlineStr">
-        <x:is>
-          <x:t>MADRID</x:t>
+          <x:t>EUROCONSULTORIA FORMACION EMPRESA, S.L.</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="121">
       <x:c r="A121" t="inlineStr">
         <x:is>
-          <x:t>25/5143</x:t>
+          <x:t>25/5499</x:t>
         </x:is>
       </x:c>
       <x:c r="B121" t="inlineStr">
         <x:is>
-          <x:t>SSCE0110</x:t>
+          <x:t>IMAI0108</x:t>
         </x:is>
       </x:c>
       <x:c r="C121" t="inlineStr">
         <x:is>
-          <x:t>HABILITACIÓN PARA LA DOCENCIA EN GRADOS A, B Y C DEL SISTEMA DE FORMACIÓN PROFESIONAL</x:t>
+          <x:t>OPERACIONES DE FONTANERÍA Y CALEFACCIÓN-CLIMATIZACIÓN DOMÉSTICA</x:t>
         </x:is>
       </x:c>
       <x:c r="D121" s="1" t="n">
         <x:v>46125.9166666667</x:v>
       </x:c>
       <x:c r="E121" s="2" t="n">
-        <x:v>46198.9166666667</x:v>
+        <x:v>46223.9166666667</x:v>
       </x:c>
       <x:c r="F121" t="inlineStr">
         <x:is>
@@ -4105,14 +4105,14 @@
       </x:c>
       <x:c r="G121" t="inlineStr">
         <x:is>
-          <x:t>EUROCONSULTORIA FORMACION EMPRESA, S.L.</x:t>
+          <x:t>CDM DESARROLLO INTEGRAL DE PROYECTOS FORMATIVOS SL</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="122">
       <x:c r="A122" t="inlineStr">
         <x:is>
-          <x:t>25/5499</x:t>
+          <x:t>25/5500</x:t>
         </x:is>
       </x:c>
       <x:c r="B122" t="inlineStr">
@@ -4129,7 +4129,7 @@
         <x:v>46125.9166666667</x:v>
       </x:c>
       <x:c r="E122" s="2" t="n">
-        <x:v>46223.9166666667</x:v>
+        <x:v>46231.9166666667</x:v>
       </x:c>
       <x:c r="F122" t="inlineStr">
         <x:is>
@@ -4145,24 +4145,24 @@
     <x:row r="123">
       <x:c r="A123" t="inlineStr">
         <x:is>
-          <x:t>25/5500</x:t>
+          <x:t>25/5982</x:t>
         </x:is>
       </x:c>
       <x:c r="B123" t="inlineStr">
         <x:is>
-          <x:t>IMAI0108</x:t>
+          <x:t>HOTA0108</x:t>
         </x:is>
       </x:c>
       <x:c r="C123" t="inlineStr">
         <x:is>
-          <x:t>OPERACIONES DE FONTANERÍA Y CALEFACCIÓN-CLIMATIZACIÓN DOMÉSTICA</x:t>
+          <x:t>OPERACIONES BÁSICAS DE PISOS EN ALOJAMIENTOS</x:t>
         </x:is>
       </x:c>
       <x:c r="D123" s="1" t="n">
         <x:v>46125.9166666667</x:v>
       </x:c>
       <x:c r="E123" s="2" t="n">
-        <x:v>46231.9166666667</x:v>
+        <x:v>46324.9583333333</x:v>
       </x:c>
       <x:c r="F123" t="inlineStr">
         <x:is>
@@ -4171,31 +4171,31 @@
       </x:c>
       <x:c r="G123" t="inlineStr">
         <x:is>
-          <x:t>CDM DESARROLLO INTEGRAL DE PROYECTOS FORMATIVOS SL</x:t>
+          <x:t>GRUPO CDM ESCUELAS PROFESIONALES S.L</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="124">
       <x:c r="A124" t="inlineStr">
         <x:is>
-          <x:t>25/5982</x:t>
+          <x:t>25/4951</x:t>
         </x:is>
       </x:c>
       <x:c r="B124" t="inlineStr">
         <x:is>
-          <x:t>HOTA0108</x:t>
+          <x:t>AFDA0111</x:t>
         </x:is>
       </x:c>
       <x:c r="C124" t="inlineStr">
         <x:is>
-          <x:t>OPERACIONES BÁSICAS DE PISOS EN ALOJAMIENTOS</x:t>
+          <x:t>FITNESS ACUÁTICO E HIDROCINESIA</x:t>
         </x:is>
       </x:c>
       <x:c r="D124" s="1" t="n">
-        <x:v>46125.9166666667</x:v>
+        <x:v>46124.9166666667</x:v>
       </x:c>
       <x:c r="E124" s="2" t="n">
-        <x:v>46324.9583333333</x:v>
+        <x:v>46286.9166666667</x:v>
       </x:c>
       <x:c r="F124" t="inlineStr">
         <x:is>
@@ -4204,7 +4204,7 @@
       </x:c>
       <x:c r="G124" t="inlineStr">
         <x:is>
-          <x:t>GRUPO CDM ESCUELAS PROFESIONALES S.L</x:t>
+          <x:t>ANGEL FERNANDEZ-ROLDAN GONZALEZ</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -4244,55 +4244,60 @@
     <x:row r="126">
       <x:c r="A126" t="inlineStr">
         <x:is>
-          <x:t>25/5359</x:t>
+          <x:t>25/5285</x:t>
         </x:is>
       </x:c>
       <x:c r="B126" t="inlineStr">
         <x:is>
-          <x:t>COML0210</x:t>
+          <x:t>IFCD0112</x:t>
         </x:is>
       </x:c>
       <x:c r="C126" t="inlineStr">
         <x:is>
-          <x:t>GESTIÓN Y CONTROL DEL APROVISIONAMIENTO</x:t>
+          <x:t>PROGRAMACIÓN CON LENGUAJES ORIENTADOS A OBJETOS Y BASES DE DATOS RELACIONALES</x:t>
         </x:is>
       </x:c>
       <x:c r="D126" s="1" t="n">
-        <x:v>46120.9166666667</x:v>
+        <x:v>46121.9166666667</x:v>
+      </x:c>
+      <x:c r="E126" s="2" t="n">
+        <x:v>46261.9166666667</x:v>
       </x:c>
       <x:c r="F126" t="inlineStr">
         <x:is>
-          <x:t>Presencial</x:t>
+          <x:t>Teleformación</x:t>
         </x:is>
       </x:c>
       <x:c r="G126" t="inlineStr">
         <x:is>
-          <x:t>SERPROFES SL</x:t>
+          <x:t>DOCENCIA Y MULTIMEDIA MADRID</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H126" t="inlineStr">
+        <x:is>
+          <x:t>MADRID</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="127">
       <x:c r="A127" t="inlineStr">
         <x:is>
-          <x:t>25/5585</x:t>
+          <x:t>25/5359</x:t>
         </x:is>
       </x:c>
       <x:c r="B127" t="inlineStr">
         <x:is>
-          <x:t>COMV0108</x:t>
+          <x:t>COML0210</x:t>
         </x:is>
       </x:c>
       <x:c r="C127" t="inlineStr">
         <x:is>
-          <x:t>ACTIVIDADES DE VENTA</x:t>
+          <x:t>GESTIÓN Y CONTROL DEL APROVISIONAMIENTO</x:t>
         </x:is>
       </x:c>
       <x:c r="D127" s="1" t="n">
         <x:v>46120.9166666667</x:v>
       </x:c>
-      <x:c r="E127" s="2" t="n">
-        <x:v>46174.9166666667</x:v>
-      </x:c>
       <x:c r="F127" t="inlineStr">
         <x:is>
           <x:t>Presencial</x:t>
@@ -4300,31 +4305,31 @@
       </x:c>
       <x:c r="G127" t="inlineStr">
         <x:is>
-          <x:t>KNOWLEDGE INNOVATION WORKS, S.L.</x:t>
+          <x:t>SERPROFES SL</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="128">
       <x:c r="A128" t="inlineStr">
         <x:is>
-          <x:t>25/5596</x:t>
+          <x:t>25/5585</x:t>
         </x:is>
       </x:c>
       <x:c r="B128" t="inlineStr">
         <x:is>
-          <x:t>HOTG0208</x:t>
+          <x:t>COMV0108</x:t>
         </x:is>
       </x:c>
       <x:c r="C128" t="inlineStr">
         <x:is>
-          <x:t>VENTA DE PRODUCTOS Y SERVICIOS TURÍSTICOS</x:t>
+          <x:t>ACTIVIDADES DE VENTA</x:t>
         </x:is>
       </x:c>
       <x:c r="D128" s="1" t="n">
         <x:v>46120.9166666667</x:v>
       </x:c>
       <x:c r="E128" s="2" t="n">
-        <x:v>46285.9166666667</x:v>
+        <x:v>46174.9166666667</x:v>
       </x:c>
       <x:c r="F128" t="inlineStr">
         <x:is>
@@ -4333,36 +4338,31 @@
       </x:c>
       <x:c r="G128" t="inlineStr">
         <x:is>
-          <x:t>Centro de Estudios Froebel, S.L.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H128" t="inlineStr">
-        <x:is>
-          <x:t>Torrejón de Ardoz</x:t>
+          <x:t>KNOWLEDGE INNOVATION WORKS, S.L.</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="129">
       <x:c r="A129" t="inlineStr">
         <x:is>
-          <x:t>25/5653</x:t>
+          <x:t>25/5596</x:t>
         </x:is>
       </x:c>
       <x:c r="B129" t="inlineStr">
         <x:is>
-          <x:t>COML0210</x:t>
+          <x:t>HOTG0208</x:t>
         </x:is>
       </x:c>
       <x:c r="C129" t="inlineStr">
         <x:is>
-          <x:t>GESTIÓN Y CONTROL DEL APROVISIONAMIENTO</x:t>
+          <x:t>VENTA DE PRODUCTOS Y SERVICIOS TURÍSTICOS</x:t>
         </x:is>
       </x:c>
       <x:c r="D129" s="1" t="n">
         <x:v>46120.9166666667</x:v>
       </x:c>
       <x:c r="E129" s="2" t="n">
-        <x:v>46196.9166666667</x:v>
+        <x:v>46285.9166666667</x:v>
       </x:c>
       <x:c r="F129" t="inlineStr">
         <x:is>
@@ -4371,31 +4371,36 @@
       </x:c>
       <x:c r="G129" t="inlineStr">
         <x:is>
-          <x:t>FORMACION INTERNACIONAL VOCACIONAL Y EMPRENDIMIENTO, S.L.</x:t>
+          <x:t>Centro de Estudios Froebel, S.L.</x:t>
         </x:is>
       </x:c>
       <x:c r="H129" t="inlineStr">
         <x:is>
-          <x:t>Alcala de Henares</x:t>
+          <x:t>Torrejón de Ardoz</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="130">
       <x:c r="A130" t="inlineStr">
         <x:is>
-          <x:t>25/2397</x:t>
+          <x:t>25/5653</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B130" t="inlineStr">
+        <x:is>
+          <x:t>COML0210</x:t>
         </x:is>
       </x:c>
       <x:c r="C130" t="inlineStr">
         <x:is>
-          <x:t>OPERACIÓN EN SISTEMAS DE COMUNICACIÓN DE VOZ Y DATOS</x:t>
+          <x:t>GESTIÓN Y CONTROL DEL APROVISIONAMIENTO</x:t>
         </x:is>
       </x:c>
       <x:c r="D130" s="1" t="n">
         <x:v>46120.9166666667</x:v>
       </x:c>
       <x:c r="E130" s="2" t="n">
-        <x:v>46267.9166666667</x:v>
+        <x:v>46196.9166666667</x:v>
       </x:c>
       <x:c r="F130" t="inlineStr">
         <x:is>
@@ -4404,31 +4409,31 @@
       </x:c>
       <x:c r="G130" t="inlineStr">
         <x:is>
-          <x:t>CENTRO DE FORMACIÓN DIGITAL SAN BLAS</x:t>
+          <x:t>FORMACION INTERNACIONAL VOCACIONAL Y EMPRENDIMIENTO, S.L.</x:t>
         </x:is>
       </x:c>
       <x:c r="H130" t="inlineStr">
         <x:is>
-          <x:t>MADRID</x:t>
+          <x:t>Alcala de Henares</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="131">
       <x:c r="A131" t="inlineStr">
         <x:is>
-          <x:t>25/2402</x:t>
+          <x:t>25/2397</x:t>
         </x:is>
       </x:c>
       <x:c r="C131" t="inlineStr">
         <x:is>
-          <x:t>PROGRAMACIÓN CON LENGUAJES ORIENTADOS A OBJETOS Y BASES DE DATOS RELACIONALES</x:t>
+          <x:t>OPERACIÓN EN SISTEMAS DE COMUNICACIÓN DE VOZ Y DATOS</x:t>
         </x:is>
       </x:c>
       <x:c r="D131" s="1" t="n">
         <x:v>46120.9166666667</x:v>
       </x:c>
       <x:c r="E131" s="2" t="n">
-        <x:v>46301.9166666667</x:v>
+        <x:v>46267.9166666667</x:v>
       </x:c>
       <x:c r="F131" t="inlineStr">
         <x:is>
@@ -4449,24 +4454,19 @@
     <x:row r="132">
       <x:c r="A132" t="inlineStr">
         <x:is>
-          <x:t>25/5424</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B132" t="inlineStr">
-        <x:is>
-          <x:t>IMSV0308</x:t>
+          <x:t>25/2402</x:t>
         </x:is>
       </x:c>
       <x:c r="C132" t="inlineStr">
         <x:is>
-          <x:t>CÁMARA DE CINE, VÍDEO Y TELEVISIÓN</x:t>
+          <x:t>PROGRAMACIÓN CON LENGUAJES ORIENTADOS A OBJETOS Y BASES DE DATOS RELACIONALES</x:t>
         </x:is>
       </x:c>
       <x:c r="D132" s="1" t="n">
-        <x:v>46119.9166666667</x:v>
+        <x:v>46120.9166666667</x:v>
       </x:c>
       <x:c r="E132" s="2" t="n">
-        <x:v>46222.9166666667</x:v>
+        <x:v>46301.9166666667</x:v>
       </x:c>
       <x:c r="F132" t="inlineStr">
         <x:is>
@@ -4475,36 +4475,36 @@
       </x:c>
       <x:c r="G132" t="inlineStr">
         <x:is>
-          <x:t>TALLER CEFORA S.L.</x:t>
+          <x:t>CENTRO DE FORMACIÓN DIGITAL SAN BLAS</x:t>
         </x:is>
       </x:c>
       <x:c r="H132" t="inlineStr">
         <x:is>
-          <x:t>Móstoles</x:t>
+          <x:t>MADRID</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="133">
       <x:c r="A133" t="inlineStr">
         <x:is>
-          <x:t>25/8065</x:t>
+          <x:t>25/5424</x:t>
         </x:is>
       </x:c>
       <x:c r="B133" t="inlineStr">
         <x:is>
-          <x:t>SSCB0209</x:t>
+          <x:t>IMSV0308</x:t>
         </x:is>
       </x:c>
       <x:c r="C133" t="inlineStr">
         <x:is>
-          <x:t>DINAMIZACIÓN DE ACTIVIDADES DE TIEMPO LIBRE EDUCATIVO INFANTIL Y JUVENIL</x:t>
+          <x:t>CÁMARA DE CINE, VÍDEO Y TELEVISIÓN</x:t>
         </x:is>
       </x:c>
       <x:c r="D133" s="1" t="n">
         <x:v>46119.9166666667</x:v>
       </x:c>
       <x:c r="E133" s="2" t="n">
-        <x:v>46189.9166666667</x:v>
+        <x:v>46222.9166666667</x:v>
       </x:c>
       <x:c r="F133" t="inlineStr">
         <x:is>
@@ -4513,31 +4513,36 @@
       </x:c>
       <x:c r="G133" t="inlineStr">
         <x:is>
-          <x:t>MOSTOLES DESARROLLO PROMOCION ECONOMICA S.A.</x:t>
+          <x:t>TALLER CEFORA S.L.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H133" t="inlineStr">
+        <x:is>
+          <x:t>Móstoles</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="134">
       <x:c r="A134" t="inlineStr">
         <x:is>
-          <x:t>25/5702</x:t>
+          <x:t>25/8065</x:t>
         </x:is>
       </x:c>
       <x:c r="B134" t="inlineStr">
         <x:is>
-          <x:t>COML0211</x:t>
+          <x:t>SSCB0209</x:t>
         </x:is>
       </x:c>
       <x:c r="C134" t="inlineStr">
         <x:is>
-          <x:t>GESTIÓN COMERCIAL Y FINANCIERA DEL TRANSPORTE POR CARRETERA</x:t>
+          <x:t>DINAMIZACIÓN DE ACTIVIDADES DE TIEMPO LIBRE EDUCATIVO INFANTIL Y JUVENIL</x:t>
         </x:is>
       </x:c>
       <x:c r="D134" s="1" t="n">
-        <x:v>46118.9583333333</x:v>
+        <x:v>46119.9166666667</x:v>
       </x:c>
       <x:c r="E134" s="2" t="n">
-        <x:v>46313.9583333333</x:v>
+        <x:v>46189.9166666667</x:v>
       </x:c>
       <x:c r="F134" t="inlineStr">
         <x:is>
@@ -4546,14 +4551,14 @@
       </x:c>
       <x:c r="G134" t="inlineStr">
         <x:is>
-          <x:t>FORMACION PARA EL DESARROLLO E INSERCION SL</x:t>
+          <x:t>MOSTOLES DESARROLLO PROMOCION ECONOMICA S.A.</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="135">
       <x:c r="A135" t="inlineStr">
         <x:is>
-          <x:t>25/5703</x:t>
+          <x:t>25/5702</x:t>
         </x:is>
       </x:c>
       <x:c r="B135" t="inlineStr">
@@ -4570,7 +4575,7 @@
         <x:v>46118.9583333333</x:v>
       </x:c>
       <x:c r="E135" s="2" t="n">
-        <x:v>46282.9583333333</x:v>
+        <x:v>46313.9583333333</x:v>
       </x:c>
       <x:c r="F135" t="inlineStr">
         <x:is>
@@ -4586,24 +4591,24 @@
     <x:row r="136">
       <x:c r="A136" t="inlineStr">
         <x:is>
-          <x:t>25/5402</x:t>
+          <x:t>25/5703</x:t>
         </x:is>
       </x:c>
       <x:c r="B136" t="inlineStr">
         <x:is>
-          <x:t>ENAE0108</x:t>
+          <x:t>COML0211</x:t>
         </x:is>
       </x:c>
       <x:c r="C136" t="inlineStr">
         <x:is>
-          <x:t>MONTAJE Y MANTENIMIENTO DE INSTALACIONES SOLARES FOTOVOLTAICAS</x:t>
+          <x:t>GESTIÓN COMERCIAL Y FINANCIERA DEL TRANSPORTE POR CARRETERA</x:t>
         </x:is>
       </x:c>
       <x:c r="D136" s="1" t="n">
-        <x:v>46118.9166666667</x:v>
+        <x:v>46118.9583333333</x:v>
       </x:c>
       <x:c r="E136" s="2" t="n">
-        <x:v>46211.9166666667</x:v>
+        <x:v>46282.9583333333</x:v>
       </x:c>
       <x:c r="F136" t="inlineStr">
         <x:is>
@@ -4612,97 +4617,97 @@
       </x:c>
       <x:c r="G136" t="inlineStr">
         <x:is>
-          <x:t>CATFA.FORMACION Y EMPLEO S.L.</x:t>
+          <x:t>FORMACION PARA EL DESARROLLO E INSERCION SL</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="137">
       <x:c r="A137" t="inlineStr">
         <x:is>
-          <x:t>25/5471</x:t>
+          <x:t>25/5402</x:t>
         </x:is>
       </x:c>
       <x:c r="B137" t="inlineStr">
         <x:is>
-          <x:t>SANT0208</x:t>
+          <x:t>ENAE0108</x:t>
         </x:is>
       </x:c>
       <x:c r="C137" t="inlineStr">
         <x:is>
-          <x:t>TRANSPORTE SANITARIO</x:t>
+          <x:t>MONTAJE Y MANTENIMIENTO DE INSTALACIONES SOLARES FOTOVOLTAICAS</x:t>
         </x:is>
       </x:c>
       <x:c r="D137" s="1" t="n">
         <x:v>46118.9166666667</x:v>
       </x:c>
       <x:c r="E137" s="2" t="n">
-        <x:v>46279.9166666667</x:v>
+        <x:v>46211.9166666667</x:v>
       </x:c>
       <x:c r="F137" t="inlineStr">
         <x:is>
-          <x:t>Teleformación</x:t>
+          <x:t>Presencial</x:t>
         </x:is>
       </x:c>
       <x:c r="G137" t="inlineStr">
         <x:is>
-          <x:t>AUTOESCUELA GALA S.L.</x:t>
+          <x:t>CATFA.FORMACION Y EMPLEO S.L.</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="138">
       <x:c r="A138" t="inlineStr">
         <x:is>
-          <x:t>25/8061</x:t>
+          <x:t>25/5471</x:t>
         </x:is>
       </x:c>
       <x:c r="B138" t="inlineStr">
         <x:is>
-          <x:t>IMPP0108</x:t>
+          <x:t>SANT0208</x:t>
         </x:is>
       </x:c>
       <x:c r="C138" t="inlineStr">
         <x:is>
-          <x:t>CUIDADOS ESTÉTICOS DE MANOS Y PIES</x:t>
+          <x:t>TRANSPORTE SANITARIO</x:t>
         </x:is>
       </x:c>
       <x:c r="D138" s="1" t="n">
         <x:v>46118.9166666667</x:v>
       </x:c>
       <x:c r="E138" s="2" t="n">
-        <x:v>46184.9166666667</x:v>
+        <x:v>46279.9166666667</x:v>
       </x:c>
       <x:c r="F138" t="inlineStr">
         <x:is>
-          <x:t>Presencial</x:t>
+          <x:t>Teleformación</x:t>
         </x:is>
       </x:c>
       <x:c r="G138" t="inlineStr">
         <x:is>
-          <x:t>MOSTOLES DESARROLLO PROMOCION ECONOMICA S.A.</x:t>
+          <x:t>AUTOESCUELA GALA S.L.</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="139">
       <x:c r="A139" t="inlineStr">
         <x:is>
-          <x:t>25/5091</x:t>
+          <x:t>25/5879</x:t>
         </x:is>
       </x:c>
       <x:c r="B139" t="inlineStr">
         <x:is>
-          <x:t>COML0109</x:t>
+          <x:t>SSCM0108</x:t>
         </x:is>
       </x:c>
       <x:c r="C139" t="inlineStr">
         <x:is>
-          <x:t>TRÁFICO DE MERCANCÍAS POR CARRETERA</x:t>
+          <x:t>LIMPIEZA DE SUPERFICIES Y MOBILIARIO EN EDIFICIOS Y LOCALES</x:t>
         </x:is>
       </x:c>
       <x:c r="D139" s="1" t="n">
-        <x:v>46117.9166666667</x:v>
+        <x:v>46118.9166666667</x:v>
       </x:c>
       <x:c r="E139" s="2" t="n">
-        <x:v>46222.9166666667</x:v>
+        <x:v>46170.9166666667</x:v>
       </x:c>
       <x:c r="F139" t="inlineStr">
         <x:is>
@@ -4711,19 +4716,14 @@
       </x:c>
       <x:c r="G139" t="inlineStr">
         <x:is>
-          <x:t>MARSDIGITAL, S.L.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H139" t="inlineStr">
-        <x:is>
-          <x:t>Madrid</x:t>
+          <x:t>CRUZ ROJA ESPAÑOLA</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="140">
       <x:c r="A140" t="inlineStr">
         <x:is>
-          <x:t>25/5417</x:t>
+          <x:t>25/8061</x:t>
         </x:is>
       </x:c>
       <x:c r="B140" t="inlineStr">
@@ -4737,10 +4737,10 @@
         </x:is>
       </x:c>
       <x:c r="D140" s="1" t="n">
-        <x:v>46113.9166666667</x:v>
+        <x:v>46118.9166666667</x:v>
       </x:c>
       <x:c r="E140" s="2" t="n">
-        <x:v>46230.9166666667</x:v>
+        <x:v>46184.9166666667</x:v>
       </x:c>
       <x:c r="F140" t="inlineStr">
         <x:is>
@@ -4749,31 +4749,31 @@
       </x:c>
       <x:c r="G140" t="inlineStr">
         <x:is>
-          <x:t>ENSEÑANZA CREATIVA DE IMAGEN PERSONALIZADA S.L.</x:t>
+          <x:t>MOSTOLES DESARROLLO PROMOCION ECONOMICA S.A.</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="141">
       <x:c r="A141" t="inlineStr">
         <x:is>
-          <x:t>25/5818</x:t>
+          <x:t>25/5091</x:t>
         </x:is>
       </x:c>
       <x:c r="B141" t="inlineStr">
         <x:is>
-          <x:t>EOCJ0110</x:t>
+          <x:t>COML0109</x:t>
         </x:is>
       </x:c>
       <x:c r="C141" t="inlineStr">
         <x:is>
-          <x:t>INSTALACIÓN DE PLACA DE YESO LAMINADO Y FALSOS TECHOS</x:t>
+          <x:t>TRÁFICO DE MERCANCÍAS POR CARRETERA</x:t>
         </x:is>
       </x:c>
       <x:c r="D141" s="1" t="n">
-        <x:v>46113.9166666667</x:v>
+        <x:v>46117.9166666667</x:v>
       </x:c>
       <x:c r="E141" s="2" t="n">
-        <x:v>46226.9166666667</x:v>
+        <x:v>46222.9166666667</x:v>
       </x:c>
       <x:c r="F141" t="inlineStr">
         <x:is>
@@ -4782,31 +4782,36 @@
       </x:c>
       <x:c r="G141" t="inlineStr">
         <x:is>
-          <x:t>FUNDACION LABORAL DE LA CONSTRUCCION</x:t>
+          <x:t>MARSDIGITAL, S.L.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H141" t="inlineStr">
+        <x:is>
+          <x:t>Madrid</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="142">
       <x:c r="A142" t="inlineStr">
         <x:is>
-          <x:t>25/5357</x:t>
+          <x:t>25/5417</x:t>
         </x:is>
       </x:c>
       <x:c r="B142" t="inlineStr">
         <x:is>
-          <x:t>IMAR0209</x:t>
+          <x:t>IMPP0108</x:t>
         </x:is>
       </x:c>
       <x:c r="C142" t="inlineStr">
         <x:is>
-          <x:t>DESARROLLO DE PROYECTOS DE INSTALACIONES FRIGORÍFICAS</x:t>
+          <x:t>CUIDADOS ESTÉTICOS DE MANOS Y PIES</x:t>
         </x:is>
       </x:c>
       <x:c r="D142" s="1" t="n">
-        <x:v>46111.9166666667</x:v>
+        <x:v>46113.9166666667</x:v>
       </x:c>
       <x:c r="E142" s="2" t="n">
-        <x:v>46222.9166666667</x:v>
+        <x:v>46230.9166666667</x:v>
       </x:c>
       <x:c r="F142" t="inlineStr">
         <x:is>
@@ -4815,36 +4820,31 @@
       </x:c>
       <x:c r="G142" t="inlineStr">
         <x:is>
-          <x:t>LONDON EDUCATION CENTER S.L.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H142" t="inlineStr">
-        <x:is>
-          <x:t>Fuenlabrada</x:t>
+          <x:t>ENSEÑANZA CREATIVA DE IMAGEN PERSONALIZADA S.L.</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="143">
       <x:c r="A143" t="inlineStr">
         <x:is>
-          <x:t>25/4953</x:t>
+          <x:t>25/5818</x:t>
         </x:is>
       </x:c>
       <x:c r="B143" t="inlineStr">
         <x:is>
-          <x:t>AFDA0311</x:t>
+          <x:t>EOCJ0110</x:t>
         </x:is>
       </x:c>
       <x:c r="C143" t="inlineStr">
         <x:is>
-          <x:t>INSTRUCCIÓN EN YOGA</x:t>
+          <x:t>INSTALACIÓN DE PLACA DE YESO LAMINADO Y FALSOS TECHOS</x:t>
         </x:is>
       </x:c>
       <x:c r="D143" s="1" t="n">
-        <x:v>46107.9583333333</x:v>
+        <x:v>46113.9166666667</x:v>
       </x:c>
       <x:c r="E143" s="2" t="n">
-        <x:v>46198.9166666667</x:v>
+        <x:v>46226.9166666667</x:v>
       </x:c>
       <x:c r="F143" t="inlineStr">
         <x:is>
@@ -4853,31 +4853,31 @@
       </x:c>
       <x:c r="G143" t="inlineStr">
         <x:is>
-          <x:t>ANGEL FERNANDEZ-ROLDAN GONZALEZ</x:t>
+          <x:t>FUNDACION LABORAL DE LA CONSTRUCCION</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="144">
       <x:c r="A144" t="inlineStr">
         <x:is>
-          <x:t>25/5547</x:t>
+          <x:t>25/5357</x:t>
         </x:is>
       </x:c>
       <x:c r="B144" t="inlineStr">
         <x:is>
-          <x:t>COMV0108</x:t>
+          <x:t>IMAR0209</x:t>
         </x:is>
       </x:c>
       <x:c r="C144" t="inlineStr">
         <x:is>
-          <x:t>ACTIVIDADES DE VENTA</x:t>
+          <x:t>DESARROLLO DE PROYECTOS DE INSTALACIONES FRIGORÍFICAS</x:t>
         </x:is>
       </x:c>
       <x:c r="D144" s="1" t="n">
-        <x:v>46107.9583333333</x:v>
+        <x:v>46111.9166666667</x:v>
       </x:c>
       <x:c r="E144" s="2" t="n">
-        <x:v>46202.9166666667</x:v>
+        <x:v>46222.9166666667</x:v>
       </x:c>
       <x:c r="F144" t="inlineStr">
         <x:is>
@@ -4886,31 +4886,36 @@
       </x:c>
       <x:c r="G144" t="inlineStr">
         <x:is>
-          <x:t>CONECTANDO LOCAL, S.L.</x:t>
+          <x:t>LONDON EDUCATION CENTER S.L.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H144" t="inlineStr">
+        <x:is>
+          <x:t>Fuenlabrada</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="145">
       <x:c r="A145" t="inlineStr">
         <x:is>
-          <x:t>23/8325</x:t>
+          <x:t>25/4953</x:t>
         </x:is>
       </x:c>
       <x:c r="B145" t="inlineStr">
         <x:is>
-          <x:t>IMAR0508</x:t>
+          <x:t>AFDA0311</x:t>
         </x:is>
       </x:c>
       <x:c r="C145" t="inlineStr">
         <x:is>
-          <x:t>DESARROLLO DE PROYECTOS DE INSTALACIONES CALORÍFICAS</x:t>
+          <x:t>INSTRUCCIÓN EN YOGA</x:t>
         </x:is>
       </x:c>
       <x:c r="D145" s="1" t="n">
-        <x:v>46106.9583333333</x:v>
+        <x:v>46107.9583333333</x:v>
       </x:c>
       <x:c r="E145" s="2" t="n">
-        <x:v>46280.9166666667</x:v>
+        <x:v>46198.9166666667</x:v>
       </x:c>
       <x:c r="F145" t="inlineStr">
         <x:is>
@@ -4919,28 +4924,28 @@
       </x:c>
       <x:c r="G145" t="inlineStr">
         <x:is>
-          <x:t>CONECTANDO LOCAL, S.L.</x:t>
+          <x:t>ANGEL FERNANDEZ-ROLDAN GONZALEZ</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="146">
       <x:c r="A146" t="inlineStr">
         <x:is>
-          <x:t>25/5544</x:t>
+          <x:t>25/5547</x:t>
         </x:is>
       </x:c>
       <x:c r="B146" t="inlineStr">
         <x:is>
-          <x:t>AGAO0308M</x:t>
+          <x:t>COMV0108</x:t>
         </x:is>
       </x:c>
       <x:c r="C146" t="inlineStr">
         <x:is>
-          <x:t>JARDINERÍA Y RESTAURACIÓN DEL PAISAJE</x:t>
+          <x:t>ACTIVIDADES DE VENTA</x:t>
         </x:is>
       </x:c>
       <x:c r="D146" s="1" t="n">
-        <x:v>46106.9583333333</x:v>
+        <x:v>46107.9583333333</x:v>
       </x:c>
       <x:c r="E146" s="2" t="n">
         <x:v>46202.9166666667</x:v>
@@ -4959,19 +4964,24 @@
     <x:row r="147">
       <x:c r="A147" t="inlineStr">
         <x:is>
-          <x:t>25/5378</x:t>
+          <x:t>23/8325</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B147" t="inlineStr">
+        <x:is>
+          <x:t>IMAR0508</x:t>
         </x:is>
       </x:c>
       <x:c r="C147" t="inlineStr">
         <x:is>
-          <x:t>GESTIÓN Y CONTROL DEL APROVISIONAMIENTO</x:t>
+          <x:t>DESARROLLO DE PROYECTOS DE INSTALACIONES CALORÍFICAS</x:t>
         </x:is>
       </x:c>
       <x:c r="D147" s="1" t="n">
-        <x:v>46105.9583333333</x:v>
+        <x:v>46106.9583333333</x:v>
       </x:c>
       <x:c r="E147" s="2" t="n">
-        <x:v>46161.9166666667</x:v>
+        <x:v>46280.9166666667</x:v>
       </x:c>
       <x:c r="F147" t="inlineStr">
         <x:is>
@@ -4980,31 +4990,31 @@
       </x:c>
       <x:c r="G147" t="inlineStr">
         <x:is>
-          <x:t>FORMACIÓN Y EDUCACIÓN INTEGRAL S.L.</x:t>
+          <x:t>CONECTANDO LOCAL, S.L.</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="148">
       <x:c r="A148" t="inlineStr">
         <x:is>
-          <x:t>25/5409</x:t>
+          <x:t>25/5544</x:t>
         </x:is>
       </x:c>
       <x:c r="B148" t="inlineStr">
         <x:is>
-          <x:t>SSCB0109</x:t>
+          <x:t>AGAO0308M</x:t>
         </x:is>
       </x:c>
       <x:c r="C148" t="inlineStr">
         <x:is>
-          <x:t>DINAMIZACIÓN COMUNITARIA</x:t>
+          <x:t>JARDINERÍA Y RESTAURACIÓN DEL PAISAJE</x:t>
         </x:is>
       </x:c>
       <x:c r="D148" s="1" t="n">
-        <x:v>46105.9583333333</x:v>
+        <x:v>46106.9583333333</x:v>
       </x:c>
       <x:c r="E148" s="2" t="n">
-        <x:v>46233.9166666667</x:v>
+        <x:v>46202.9166666667</x:v>
       </x:c>
       <x:c r="F148" t="inlineStr">
         <x:is>
@@ -5013,64 +5023,59 @@
       </x:c>
       <x:c r="G148" t="inlineStr">
         <x:is>
-          <x:t>INNOVACION Y DESARROLLO LOCAL, S.L.</x:t>
+          <x:t>CONECTANDO LOCAL, S.L.</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="149">
       <x:c r="A149" t="inlineStr">
         <x:is>
-          <x:t>25/5443</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B149" t="inlineStr">
-        <x:is>
-          <x:t>IFCD0110</x:t>
+          <x:t>25/5378</x:t>
         </x:is>
       </x:c>
       <x:c r="C149" t="inlineStr">
         <x:is>
-          <x:t>CONFECCIÓN Y PUBLICACIÓN DE PÁGINAS WEB</x:t>
+          <x:t>GESTIÓN Y CONTROL DEL APROVISIONAMIENTO</x:t>
         </x:is>
       </x:c>
       <x:c r="D149" s="1" t="n">
         <x:v>46105.9583333333</x:v>
       </x:c>
       <x:c r="E149" s="2" t="n">
-        <x:v>46292.9166666667</x:v>
+        <x:v>46161.9166666667</x:v>
       </x:c>
       <x:c r="F149" t="inlineStr">
         <x:is>
-          <x:t>Teleformación</x:t>
+          <x:t>Presencial</x:t>
         </x:is>
       </x:c>
       <x:c r="G149" t="inlineStr">
         <x:is>
-          <x:t>CORE NETWORKS, S.L.</x:t>
+          <x:t>FORMACIÓN Y EDUCACIÓN INTEGRAL S.L.</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="150">
       <x:c r="A150" t="inlineStr">
         <x:is>
-          <x:t>25/5445</x:t>
+          <x:t>25/5409</x:t>
         </x:is>
       </x:c>
       <x:c r="B150" t="inlineStr">
         <x:is>
-          <x:t>IFCD0210</x:t>
+          <x:t>SSCB0109</x:t>
         </x:is>
       </x:c>
       <x:c r="C150" t="inlineStr">
         <x:is>
-          <x:t>DESARROLLO DE APLICACIONES CON TECNOLOGÍAS WEB</x:t>
+          <x:t>DINAMIZACIÓN COMUNITARIA</x:t>
         </x:is>
       </x:c>
       <x:c r="D150" s="1" t="n">
         <x:v>46105.9583333333</x:v>
       </x:c>
       <x:c r="E150" s="2" t="n">
-        <x:v>46292.9166666667</x:v>
+        <x:v>46233.9166666667</x:v>
       </x:c>
       <x:c r="F150" t="inlineStr">
         <x:is>
@@ -5079,156 +5084,156 @@
       </x:c>
       <x:c r="G150" t="inlineStr">
         <x:is>
-          <x:t>CORE NETWORKS, S.L.</x:t>
+          <x:t>INNOVACION Y DESARROLLO LOCAL, S.L.</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="151">
       <x:c r="A151" t="inlineStr">
         <x:is>
-          <x:t>25/5494</x:t>
+          <x:t>25/5443</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B151" t="inlineStr">
+        <x:is>
+          <x:t>IFCD0110</x:t>
         </x:is>
       </x:c>
       <x:c r="C151" t="inlineStr">
         <x:is>
-          <x:t>ATENCIÓN SANITARIA A MÚLTIPLES VÍCTIMAS Y CATÁSTROFES</x:t>
+          <x:t>CONFECCIÓN Y PUBLICACIÓN DE PÁGINAS WEB</x:t>
         </x:is>
       </x:c>
       <x:c r="D151" s="1" t="n">
         <x:v>46105.9583333333</x:v>
       </x:c>
       <x:c r="E151" s="2" t="n">
-        <x:v>46211.9166666667</x:v>
+        <x:v>46292.9166666667</x:v>
       </x:c>
       <x:c r="F151" t="inlineStr">
         <x:is>
-          <x:t>Presencial</x:t>
+          <x:t>Teleformación</x:t>
         </x:is>
       </x:c>
       <x:c r="G151" t="inlineStr">
         <x:is>
-          <x:t>FORMAJOBS S.L.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H151" t="inlineStr">
-        <x:is>
-          <x:t>Leganés</x:t>
+          <x:t>CORE NETWORKS, S.L.</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="152">
       <x:c r="A152" t="inlineStr">
         <x:is>
-          <x:t>25/5588</x:t>
+          <x:t>25/5445</x:t>
         </x:is>
       </x:c>
       <x:c r="B152" t="inlineStr">
         <x:is>
-          <x:t>SSCB0110</x:t>
+          <x:t>IFCD0210</x:t>
         </x:is>
       </x:c>
       <x:c r="C152" t="inlineStr">
         <x:is>
-          <x:t>DINAMIZACIÓN, PROGRAMACIÓN Y DESARROLLO DE ACCIONES CULTURALES</x:t>
+          <x:t>DESARROLLO DE APLICACIONES CON TECNOLOGÍAS WEB</x:t>
         </x:is>
       </x:c>
       <x:c r="D152" s="1" t="n">
         <x:v>46105.9583333333</x:v>
       </x:c>
       <x:c r="E152" s="2" t="n">
-        <x:v>46226.9166666667</x:v>
+        <x:v>46292.9166666667</x:v>
       </x:c>
       <x:c r="F152" t="inlineStr">
         <x:is>
-          <x:t>Teleformación</x:t>
+          <x:t>Presencial</x:t>
         </x:is>
       </x:c>
       <x:c r="G152" t="inlineStr">
         <x:is>
-          <x:t>KNOWLEDGE INNOVATION WORKS, S.L.</x:t>
+          <x:t>CORE NETWORKS, S.L.</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="153">
       <x:c r="A153" t="inlineStr">
         <x:is>
-          <x:t>25/5612</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B153" t="inlineStr">
-        <x:is>
-          <x:t>COMP0108</x:t>
+          <x:t>25/5494</x:t>
         </x:is>
       </x:c>
       <x:c r="C153" t="inlineStr">
         <x:is>
-          <x:t>IMPLANTACIÓN Y ANIMACIÓN DE ESPACIOS COMERCIALES</x:t>
+          <x:t>ATENCIÓN SANITARIA A MÚLTIPLES VÍCTIMAS Y CATÁSTROFES</x:t>
         </x:is>
       </x:c>
       <x:c r="D153" s="1" t="n">
         <x:v>46105.9583333333</x:v>
       </x:c>
       <x:c r="E153" s="2" t="n">
-        <x:v>46195.9166666667</x:v>
+        <x:v>46211.9166666667</x:v>
       </x:c>
       <x:c r="F153" t="inlineStr">
         <x:is>
-          <x:t>Teleformación</x:t>
+          <x:t>Presencial</x:t>
         </x:is>
       </x:c>
       <x:c r="G153" t="inlineStr">
         <x:is>
-          <x:t>CENTRO DE ENSEÑANZA OCUPACIONAL, S.L.</x:t>
+          <x:t>FORMAJOBS S.L.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H153" t="inlineStr">
+        <x:is>
+          <x:t>Leganés</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="154">
       <x:c r="A154" t="inlineStr">
         <x:is>
-          <x:t>25/5721</x:t>
+          <x:t>25/5588</x:t>
         </x:is>
       </x:c>
       <x:c r="B154" t="inlineStr">
         <x:is>
-          <x:t>ELEE0210</x:t>
+          <x:t>SSCB0110</x:t>
         </x:is>
       </x:c>
       <x:c r="C154" t="inlineStr">
         <x:is>
-          <x:t>DESARROLLO DE PROYECTOS DE REDES ELÉCTRICAS DE BAJA Y ALTA TENSIÓN</x:t>
+          <x:t>DINAMIZACIÓN, PROGRAMACIÓN Y DESARROLLO DE ACCIONES CULTURALES</x:t>
         </x:is>
       </x:c>
       <x:c r="D154" s="1" t="n">
         <x:v>46105.9583333333</x:v>
       </x:c>
       <x:c r="E154" s="2" t="n">
-        <x:v>46226.9583333333</x:v>
+        <x:v>46226.9166666667</x:v>
       </x:c>
       <x:c r="F154" t="inlineStr">
         <x:is>
-          <x:t>Presencial</x:t>
+          <x:t>Teleformación</x:t>
         </x:is>
       </x:c>
       <x:c r="G154" t="inlineStr">
         <x:is>
-          <x:t>SOLUCIONES CONSULTORAS FORMATIVAS C.C.R. SL UNIPERSONAL</x:t>
+          <x:t>KNOWLEDGE INNOVATION WORKS, S.L.</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="155">
       <x:c r="A155" t="inlineStr">
         <x:is>
-          <x:t>25/5835</x:t>
+          <x:t>25/5612</x:t>
         </x:is>
       </x:c>
       <x:c r="B155" t="inlineStr">
         <x:is>
-          <x:t>AGAO0208</x:t>
+          <x:t>COMP0108</x:t>
         </x:is>
       </x:c>
       <x:c r="C155" t="inlineStr">
         <x:is>
-          <x:t>INSTALACIÓN Y MANTENIMIENTO DE JARDINES Y ZONAS VERDES</x:t>
+          <x:t>IMPLANTACIÓN Y ANIMACIÓN DE ESPACIOS COMERCIALES</x:t>
         </x:is>
       </x:c>
       <x:c r="D155" s="1" t="n">
@@ -5239,36 +5244,36 @@
       </x:c>
       <x:c r="F155" t="inlineStr">
         <x:is>
-          <x:t>Presencial</x:t>
+          <x:t>Teleformación</x:t>
         </x:is>
       </x:c>
       <x:c r="G155" t="inlineStr">
         <x:is>
-          <x:t>ARACOVE</x:t>
+          <x:t>CENTRO DE ENSEÑANZA OCUPACIONAL, S.L.</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="156">
       <x:c r="A156" t="inlineStr">
         <x:is>
-          <x:t>25/5066</x:t>
+          <x:t>25/5721</x:t>
         </x:is>
       </x:c>
       <x:c r="B156" t="inlineStr">
         <x:is>
-          <x:t>FMEC0208</x:t>
+          <x:t>ELEE0210</x:t>
         </x:is>
       </x:c>
       <x:c r="C156" t="inlineStr">
         <x:is>
-          <x:t>DISEÑO DE CALDERERÍA Y ESTRUCTURAS METÁLICAS</x:t>
+          <x:t>DESARROLLO DE PROYECTOS DE REDES ELÉCTRICAS DE BAJA Y ALTA TENSIÓN</x:t>
         </x:is>
       </x:c>
       <x:c r="D156" s="1" t="n">
-        <x:v>46104.9583333333</x:v>
+        <x:v>46105.9583333333</x:v>
       </x:c>
       <x:c r="E156" s="2" t="n">
-        <x:v>46289.9166666667</x:v>
+        <x:v>46226.9583333333</x:v>
       </x:c>
       <x:c r="F156" t="inlineStr">
         <x:is>
@@ -5277,36 +5282,31 @@
       </x:c>
       <x:c r="G156" t="inlineStr">
         <x:is>
-          <x:t>CAMPUS INNOVACION Y GESTION SL</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H156" t="inlineStr">
-        <x:is>
-          <x:t>MADRID</x:t>
+          <x:t>SOLUCIONES CONSULTORAS FORMATIVAS C.C.R. SL UNIPERSONAL</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="157">
       <x:c r="A157" t="inlineStr">
         <x:is>
-          <x:t>25/5498</x:t>
+          <x:t>25/5835</x:t>
         </x:is>
       </x:c>
       <x:c r="B157" t="inlineStr">
         <x:is>
-          <x:t>SSCS0108</x:t>
+          <x:t>AGAO0208</x:t>
         </x:is>
       </x:c>
       <x:c r="C157" t="inlineStr">
         <x:is>
-          <x:t>ATENCIÓN SOCIOSANITARIA A PERSONAS EN EL DOMICILIO</x:t>
+          <x:t>INSTALACIÓN Y MANTENIMIENTO DE JARDINES Y ZONAS VERDES</x:t>
         </x:is>
       </x:c>
       <x:c r="D157" s="1" t="n">
-        <x:v>46104.9583333333</x:v>
+        <x:v>46105.9583333333</x:v>
       </x:c>
       <x:c r="E157" s="2" t="n">
-        <x:v>46194.9166666667</x:v>
+        <x:v>46195.9166666667</x:v>
       </x:c>
       <x:c r="F157" t="inlineStr">
         <x:is>
@@ -5315,158 +5315,163 @@
       </x:c>
       <x:c r="G157" t="inlineStr">
         <x:is>
-          <x:t>FORMAJOBS S.L.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H157" t="inlineStr">
-        <x:is>
-          <x:t>Leganés</x:t>
+          <x:t>ARACOVE</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="158">
       <x:c r="A158" t="inlineStr">
         <x:is>
-          <x:t>25/5609</x:t>
+          <x:t>25/5066</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B158" t="inlineStr">
+        <x:is>
+          <x:t>FMEC0208</x:t>
         </x:is>
       </x:c>
       <x:c r="C158" t="inlineStr">
         <x:is>
-          <x:t>ASISTENCIA EN LA GESTIÓN DE LOS PROCEDIMIENTOS TRIBUTARIOS</x:t>
+          <x:t>DISEÑO DE CALDERERÍA Y ESTRUCTURAS METÁLICAS</x:t>
         </x:is>
       </x:c>
       <x:c r="D158" s="1" t="n">
         <x:v>46104.9583333333</x:v>
       </x:c>
       <x:c r="E158" s="2" t="n">
-        <x:v>46227.9166666667</x:v>
+        <x:v>46289.9166666667</x:v>
       </x:c>
       <x:c r="F158" t="inlineStr">
         <x:is>
-          <x:t>Teleformación</x:t>
+          <x:t>Presencial</x:t>
         </x:is>
       </x:c>
       <x:c r="G158" t="inlineStr">
         <x:is>
-          <x:t>CENTRO DE ENSEÑANZA OCUPACIONAL, S.L.</x:t>
+          <x:t>CAMPUS INNOVACION Y GESTION SL</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H158" t="inlineStr">
+        <x:is>
+          <x:t>MADRID</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="159">
       <x:c r="A159" t="inlineStr">
         <x:is>
-          <x:t>25/5610</x:t>
+          <x:t>25/5498</x:t>
         </x:is>
       </x:c>
       <x:c r="B159" t="inlineStr">
         <x:is>
-          <x:t>ADGD0210</x:t>
+          <x:t>SSCS0108</x:t>
         </x:is>
       </x:c>
       <x:c r="C159" t="inlineStr">
         <x:is>
-          <x:t>CREACIÓN Y GESTIÓN DE MICROEMPRESAS</x:t>
+          <x:t>ATENCIÓN SOCIOSANITARIA A PERSONAS EN EL DOMICILIO</x:t>
         </x:is>
       </x:c>
       <x:c r="D159" s="1" t="n">
         <x:v>46104.9583333333</x:v>
       </x:c>
       <x:c r="E159" s="2" t="n">
-        <x:v>46224.9166666667</x:v>
+        <x:v>46194.9166666667</x:v>
       </x:c>
       <x:c r="F159" t="inlineStr">
         <x:is>
-          <x:t>Teleformación</x:t>
+          <x:t>Presencial</x:t>
         </x:is>
       </x:c>
       <x:c r="G159" t="inlineStr">
         <x:is>
-          <x:t>CENTRO DE ENSEÑANZA OCUPACIONAL, S.L.</x:t>
+          <x:t>FORMAJOBS S.L.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H159" t="inlineStr">
+        <x:is>
+          <x:t>Leganés</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="160">
       <x:c r="A160" t="inlineStr">
         <x:is>
-          <x:t>25/9015</x:t>
+          <x:t>25/5609</x:t>
         </x:is>
       </x:c>
       <x:c r="C160" t="inlineStr">
         <x:is>
-          <x:t>DESARROLLO DE APLICACIONES CON TECNOLOGÍAS WEB</x:t>
+          <x:t>ASISTENCIA EN LA GESTIÓN DE LOS PROCEDIMIENTOS TRIBUTARIOS</x:t>
         </x:is>
       </x:c>
       <x:c r="D160" s="1" t="n">
         <x:v>46104.9583333333</x:v>
       </x:c>
       <x:c r="E160" s="2" t="n">
-        <x:v>46223.9166666667</x:v>
+        <x:v>46227.9166666667</x:v>
       </x:c>
       <x:c r="F160" t="inlineStr">
         <x:is>
-          <x:t>Presencial</x:t>
+          <x:t>Teleformación</x:t>
         </x:is>
       </x:c>
       <x:c r="G160" t="inlineStr">
         <x:is>
-          <x:t>CEFORA S.L.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H160" t="inlineStr">
-        <x:is>
-          <x:t>MOSTOLES</x:t>
+          <x:t>CENTRO DE ENSEÑANZA OCUPACIONAL, S.L.</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="161">
       <x:c r="A161" t="inlineStr">
         <x:is>
-          <x:t>23/8437</x:t>
+          <x:t>25/5610</x:t>
         </x:is>
       </x:c>
       <x:c r="B161" t="inlineStr">
         <x:is>
-          <x:t>EOCB0109</x:t>
+          <x:t>ADGD0210</x:t>
         </x:is>
       </x:c>
       <x:c r="C161" t="inlineStr">
         <x:is>
-          <x:t>OPERACIONES AUXILIARES DE REVESTIMIENTOS CONTINUOS EN CONSTRUCCIÓN</x:t>
+          <x:t>CREACIÓN Y GESTIÓN DE MICROEMPRESAS</x:t>
         </x:is>
       </x:c>
       <x:c r="D161" s="1" t="n">
-        <x:v>46103.9583333333</x:v>
+        <x:v>46104.9583333333</x:v>
       </x:c>
       <x:c r="E161" s="2" t="n">
-        <x:v>46208.9166666667</x:v>
+        <x:v>46224.9166666667</x:v>
       </x:c>
       <x:c r="F161" t="inlineStr">
         <x:is>
-          <x:t>Presencial</x:t>
+          <x:t>Teleformación</x:t>
         </x:is>
       </x:c>
       <x:c r="G161" t="inlineStr">
         <x:is>
-          <x:t>ARACOVE</x:t>
+          <x:t>CENTRO DE ENSEÑANZA OCUPACIONAL, S.L.</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="162">
       <x:c r="A162" t="inlineStr">
         <x:is>
-          <x:t>25/2153</x:t>
+          <x:t>25/9015</x:t>
         </x:is>
       </x:c>
       <x:c r="C162" t="inlineStr">
         <x:is>
-          <x:t>DESARROLLO DE APLICACIONES CON TECNOLOGÍA WEB</x:t>
+          <x:t>DESARROLLO DE APLICACIONES CON TECNOLOGÍAS WEB</x:t>
         </x:is>
       </x:c>
       <x:c r="D162" s="1" t="n">
-        <x:v>46103.9583333333</x:v>
+        <x:v>46104.9583333333</x:v>
       </x:c>
       <x:c r="E162" s="2" t="n">
-        <x:v>46216.9166666667</x:v>
+        <x:v>46223.9166666667</x:v>
       </x:c>
       <x:c r="F162" t="inlineStr">
         <x:is>
@@ -5475,36 +5480,36 @@
       </x:c>
       <x:c r="G162" t="inlineStr">
         <x:is>
-          <x:t>CENTRO DE FORMACIÓN DIGITAL ALCOBENDAS</x:t>
+          <x:t>CEFORA S.L.</x:t>
         </x:is>
       </x:c>
       <x:c r="H162" t="inlineStr">
         <x:is>
-          <x:t>ALCOBENDAS</x:t>
+          <x:t>MOSTOLES</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="163">
       <x:c r="A163" t="inlineStr">
         <x:is>
-          <x:t>25/4952</x:t>
+          <x:t>23/8437</x:t>
         </x:is>
       </x:c>
       <x:c r="B163" t="inlineStr">
         <x:is>
-          <x:t>AFDA0310</x:t>
+          <x:t>EOCB0109</x:t>
         </x:is>
       </x:c>
       <x:c r="C163" t="inlineStr">
         <x:is>
-          <x:t>ACTIVIDADES DE NATACIÓN</x:t>
+          <x:t>OPERACIONES AUXILIARES DE REVESTIMIENTOS CONTINUOS EN CONSTRUCCIÓN</x:t>
         </x:is>
       </x:c>
       <x:c r="D163" s="1" t="n">
         <x:v>46103.9583333333</x:v>
       </x:c>
       <x:c r="E163" s="2" t="n">
-        <x:v>46273.9166666667</x:v>
+        <x:v>46208.9166666667</x:v>
       </x:c>
       <x:c r="F163" t="inlineStr">
         <x:is>
@@ -5513,69 +5518,64 @@
       </x:c>
       <x:c r="G163" t="inlineStr">
         <x:is>
-          <x:t>ANGEL FERNANDEZ-ROLDAN GONZALEZ</x:t>
+          <x:t>ARACOVE</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="164">
       <x:c r="A164" t="inlineStr">
         <x:is>
-          <x:t>25/5286</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B164" t="inlineStr">
-        <x:is>
-          <x:t>IFCD0211</x:t>
+          <x:t>25/2153</x:t>
         </x:is>
       </x:c>
       <x:c r="C164" t="inlineStr">
         <x:is>
-          <x:t>SISTEMAS DE GESTIÓN DE INFORMACIÓN</x:t>
+          <x:t>DESARROLLO DE APLICACIONES CON TECNOLOGÍA WEB</x:t>
         </x:is>
       </x:c>
       <x:c r="D164" s="1" t="n">
         <x:v>46103.9583333333</x:v>
       </x:c>
       <x:c r="E164" s="2" t="n">
-        <x:v>46264.9166666667</x:v>
+        <x:v>46216.9166666667</x:v>
       </x:c>
       <x:c r="F164" t="inlineStr">
         <x:is>
-          <x:t>Teleformación</x:t>
+          <x:t>Presencial</x:t>
         </x:is>
       </x:c>
       <x:c r="G164" t="inlineStr">
         <x:is>
-          <x:t>DOCENCIA Y MULTIMEDIA MADRID</x:t>
+          <x:t>CENTRO DE FORMACIÓN DIGITAL ALCOBENDAS</x:t>
         </x:is>
       </x:c>
       <x:c r="H164" t="inlineStr">
         <x:is>
-          <x:t>MADRID</x:t>
+          <x:t>ALCOBENDAS</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="165">
       <x:c r="A165" t="inlineStr">
         <x:is>
-          <x:t>25/5251</x:t>
+          <x:t>25/4952</x:t>
         </x:is>
       </x:c>
       <x:c r="B165" t="inlineStr">
         <x:is>
-          <x:t>AFDA0110</x:t>
+          <x:t>AFDA0310</x:t>
         </x:is>
       </x:c>
       <x:c r="C165" t="inlineStr">
         <x:is>
-          <x:t>ACONDICIONAMIENTO FÍSICO EN GRUPO CON SOPORTE MUSICAL</x:t>
+          <x:t>ACTIVIDADES DE NATACIÓN</x:t>
         </x:is>
       </x:c>
       <x:c r="D165" s="1" t="n">
-        <x:v>46100.9583333333</x:v>
+        <x:v>46103.9583333333</x:v>
       </x:c>
       <x:c r="E165" s="2" t="n">
-        <x:v>46294.9166666667</x:v>
+        <x:v>46273.9166666667</x:v>
       </x:c>
       <x:c r="F165" t="inlineStr">
         <x:is>
@@ -5584,94 +5584,102 @@
       </x:c>
       <x:c r="G165" t="inlineStr">
         <x:is>
-          <x:t>SERVIOCIO BEONE BOADILLA, S.L.U.</x:t>
+          <x:t>ANGEL FERNANDEZ-ROLDAN GONZALEZ</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="166">
       <x:c r="A166" t="inlineStr">
         <x:is>
-          <x:t>25/5633</x:t>
+          <x:t>25/5286</x:t>
         </x:is>
       </x:c>
       <x:c r="B166" t="inlineStr">
         <x:is>
-          <x:t>IMSV0308</x:t>
+          <x:t>IFCD0211</x:t>
         </x:is>
       </x:c>
       <x:c r="C166" t="inlineStr">
         <x:is>
-          <x:t>CÁMARA DE CINE, VÍDEO Y TELEVISIÓN</x:t>
+          <x:t>SISTEMAS DE GESTIÓN DE INFORMACIÓN</x:t>
         </x:is>
       </x:c>
       <x:c r="D166" s="1" t="n">
-        <x:v>46100.9583333333</x:v>
+        <x:v>46103.9583333333</x:v>
       </x:c>
       <x:c r="E166" s="2" t="n">
-        <x:v>46194.9166666667</x:v>
+        <x:v>46264.9166666667</x:v>
       </x:c>
       <x:c r="F166" t="inlineStr">
         <x:is>
-          <x:t>Presencial</x:t>
+          <x:t>Teleformación</x:t>
         </x:is>
       </x:c>
       <x:c r="G166" t="inlineStr">
         <x:is>
-          <x:t>EMPRENDE Y GESTIONA 2015, S.L.</x:t>
+          <x:t>DOCENCIA Y MULTIMEDIA MADRID</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H166" t="inlineStr">
+        <x:is>
+          <x:t>MADRID</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="167">
       <x:c r="A167" t="inlineStr">
         <x:is>
-          <x:t>25/4985</x:t>
+          <x:t>25/5251</x:t>
         </x:is>
       </x:c>
       <x:c r="B167" t="inlineStr">
         <x:is>
-          <x:t>ADGG0408</x:t>
+          <x:t>AFDA0110</x:t>
         </x:is>
       </x:c>
       <x:c r="C167" t="inlineStr">
         <x:is>
-          <x:t>OPERACIONES AUXILIARES DE SERVICIOS ADMINISTRATIVOS Y GENERALES</x:t>
+          <x:t>ACONDICIONAMIENTO FÍSICO EN GRUPO CON SOPORTE MUSICAL</x:t>
         </x:is>
       </x:c>
       <x:c r="D167" s="1" t="n">
-        <x:v>46099.9583333333</x:v>
+        <x:v>46100.9583333333</x:v>
+      </x:c>
+      <x:c r="E167" s="2" t="n">
+        <x:v>46294.9166666667</x:v>
       </x:c>
       <x:c r="F167" t="inlineStr">
         <x:is>
-          <x:t>Teleformación</x:t>
+          <x:t>Presencial</x:t>
         </x:is>
       </x:c>
       <x:c r="G167" t="inlineStr">
         <x:is>
-          <x:t>CENTRO DE ESTUDIOS ADAMS EDICIONES VALBUENA, S.A.</x:t>
+          <x:t>SERVIOCIO BEONE BOADILLA, S.L.U.</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="168">
       <x:c r="A168" t="inlineStr">
         <x:is>
-          <x:t>25/5582</x:t>
+          <x:t>25/5284</x:t>
         </x:is>
       </x:c>
       <x:c r="B168" t="inlineStr">
         <x:is>
-          <x:t>COMT0112</x:t>
+          <x:t>COMM0111</x:t>
         </x:is>
       </x:c>
       <x:c r="C168" t="inlineStr">
         <x:is>
-          <x:t>ACTIVIDADES DE GESTIÓN DEL PEQUEÑO COMERCIO</x:t>
+          <x:t>ASISTENCIA A LA INVESTIGACIÓN DE MERCADOS</x:t>
         </x:is>
       </x:c>
       <x:c r="D168" s="1" t="n">
-        <x:v>46099.9583333333</x:v>
+        <x:v>46100.9583333333</x:v>
       </x:c>
       <x:c r="E168" s="2" t="n">
-        <x:v>46195.9166666667</x:v>
+        <x:v>46187.9166666667</x:v>
       </x:c>
       <x:c r="F168" t="inlineStr">
         <x:is>
@@ -5680,31 +5688,36 @@
       </x:c>
       <x:c r="G168" t="inlineStr">
         <x:is>
-          <x:t>KNOWLEDGE INNOVATION WORKS, S.L.</x:t>
+          <x:t>DOCENCIA Y MULTIMEDIA MADRID</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H168" t="inlineStr">
+        <x:is>
+          <x:t>MADRID</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="169">
       <x:c r="A169" t="inlineStr">
         <x:is>
-          <x:t>23/8291</x:t>
+          <x:t>25/5633</x:t>
         </x:is>
       </x:c>
       <x:c r="B169" t="inlineStr">
         <x:is>
-          <x:t>IFCT0510</x:t>
+          <x:t>IMSV0308</x:t>
         </x:is>
       </x:c>
       <x:c r="C169" t="inlineStr">
         <x:is>
-          <x:t>GESTIÓN DE SISTEMAS INFORMÁTICOS</x:t>
+          <x:t>CÁMARA DE CINE, VÍDEO Y TELEVISIÓN</x:t>
         </x:is>
       </x:c>
       <x:c r="D169" s="1" t="n">
-        <x:v>46098.9583333333</x:v>
+        <x:v>46100.9583333333</x:v>
       </x:c>
       <x:c r="E169" s="2" t="n">
-        <x:v>46229.9166666667</x:v>
+        <x:v>46194.9166666667</x:v>
       </x:c>
       <x:c r="F169" t="inlineStr">
         <x:is>
@@ -5713,57 +5726,49 @@
       </x:c>
       <x:c r="G169" t="inlineStr">
         <x:is>
-          <x:t>FORMAJOBS S.L.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H169" t="inlineStr">
-        <x:is>
-          <x:t>Leganés</x:t>
+          <x:t>EMPRENDE Y GESTIONA 2015, S.L.</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="170">
       <x:c r="A170" t="inlineStr">
         <x:is>
-          <x:t>25/5496</x:t>
+          <x:t>25/4985</x:t>
         </x:is>
       </x:c>
       <x:c r="B170" t="inlineStr">
         <x:is>
-          <x:t>SEAG0209</x:t>
+          <x:t>ADGG0408</x:t>
         </x:is>
       </x:c>
       <x:c r="C170" t="inlineStr">
         <x:is>
-          <x:t>LIMPIEZA EN ESPACIOS ABIERTOS E INSTALACIONES INDUSTRIALES</x:t>
+          <x:t>OPERACIONES AUXILIARES DE SERVICIOS ADMINISTRATIVOS Y GENERALES</x:t>
         </x:is>
       </x:c>
       <x:c r="D170" s="1" t="n">
-        <x:v>46098.9583333333</x:v>
-      </x:c>
-      <x:c r="E170" s="2" t="n">
-        <x:v>46197.9166666667</x:v>
+        <x:v>46099.9583333333</x:v>
       </x:c>
       <x:c r="F170" t="inlineStr">
         <x:is>
-          <x:t>Presencial</x:t>
+          <x:t>Teleformación</x:t>
         </x:is>
       </x:c>
       <x:c r="G170" t="inlineStr">
         <x:is>
-          <x:t>FORMAJOBS S.L.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H170" t="inlineStr">
-        <x:is>
-          <x:t>Leganés</x:t>
+          <x:t>CENTRO DE ESTUDIOS ADAMS EDICIONES VALBUENA, S.A.</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="171">
       <x:c r="A171" t="inlineStr">
         <x:is>
-          <x:t>25/5546</x:t>
+          <x:t>25/5582</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B171" t="inlineStr">
+        <x:is>
+          <x:t>COMT0112</x:t>
         </x:is>
       </x:c>
       <x:c r="C171" t="inlineStr">
@@ -5772,10 +5777,10 @@
         </x:is>
       </x:c>
       <x:c r="D171" s="1" t="n">
-        <x:v>46098.9583333333</x:v>
+        <x:v>46099.9583333333</x:v>
       </x:c>
       <x:c r="E171" s="2" t="n">
-        <x:v>46169.9166666667</x:v>
+        <x:v>46195.9166666667</x:v>
       </x:c>
       <x:c r="F171" t="inlineStr">
         <x:is>
@@ -5784,102 +5789,102 @@
       </x:c>
       <x:c r="G171" t="inlineStr">
         <x:is>
-          <x:t>CONECTANDO LOCAL, S.L.</x:t>
+          <x:t>KNOWLEDGE INNOVATION WORKS, S.L.</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="172">
       <x:c r="A172" t="inlineStr">
         <x:is>
-          <x:t>25/5548</x:t>
+          <x:t>23/8291</x:t>
         </x:is>
       </x:c>
       <x:c r="B172" t="inlineStr">
         <x:is>
-          <x:t>HOTI0108</x:t>
+          <x:t>IFCT0510</x:t>
         </x:is>
       </x:c>
       <x:c r="C172" t="inlineStr">
         <x:is>
-          <x:t>PROMOCIÓN TURÍSTICA LOCAL E INFORMACIÓN AL VISITANTE</x:t>
+          <x:t>GESTIÓN DE SISTEMAS INFORMÁTICOS</x:t>
         </x:is>
       </x:c>
       <x:c r="D172" s="1" t="n">
         <x:v>46098.9583333333</x:v>
       </x:c>
       <x:c r="E172" s="2" t="n">
-        <x:v>46287.9166666667</x:v>
+        <x:v>46229.9166666667</x:v>
       </x:c>
       <x:c r="F172" t="inlineStr">
         <x:is>
-          <x:t>Teleformación</x:t>
+          <x:t>Presencial</x:t>
         </x:is>
       </x:c>
       <x:c r="G172" t="inlineStr">
         <x:is>
-          <x:t>CONECTANDO LOCAL, S.L.</x:t>
+          <x:t>FORMAJOBS S.L.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H172" t="inlineStr">
+        <x:is>
+          <x:t>Leganés</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="173">
       <x:c r="A173" t="inlineStr">
         <x:is>
-          <x:t>25/5559</x:t>
+          <x:t>25/5496</x:t>
         </x:is>
       </x:c>
       <x:c r="B173" t="inlineStr">
         <x:is>
-          <x:t>HOTR0109</x:t>
+          <x:t>SEAG0209</x:t>
         </x:is>
       </x:c>
       <x:c r="C173" t="inlineStr">
         <x:is>
-          <x:t>OPERACIONES BÁSICAS DE PASTELERÍA</x:t>
+          <x:t>LIMPIEZA EN ESPACIOS ABIERTOS E INSTALACIONES INDUSTRIALES</x:t>
         </x:is>
       </x:c>
       <x:c r="D173" s="1" t="n">
         <x:v>46098.9583333333</x:v>
       </x:c>
       <x:c r="E173" s="2" t="n">
-        <x:v>46196.9166666667</x:v>
+        <x:v>46197.9166666667</x:v>
       </x:c>
       <x:c r="F173" t="inlineStr">
         <x:is>
-          <x:t>Teleformación</x:t>
+          <x:t>Presencial</x:t>
         </x:is>
       </x:c>
       <x:c r="G173" t="inlineStr">
         <x:is>
-          <x:t>CENTRO ARANDA SCHOLA SL</x:t>
+          <x:t>FORMAJOBS S.L.</x:t>
         </x:is>
       </x:c>
       <x:c r="H173" t="inlineStr">
         <x:is>
-          <x:t>MADRID</x:t>
+          <x:t>Leganés</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="174">
       <x:c r="A174" t="inlineStr">
         <x:is>
-          <x:t>25/5629</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B174" t="inlineStr">
-        <x:is>
-          <x:t>ENAS0110</x:t>
+          <x:t>25/5546</x:t>
         </x:is>
       </x:c>
       <x:c r="C174" t="inlineStr">
         <x:is>
-          <x:t>MONTAJE, PUESTA EN SERVICIO, MANTENIMIENTO, INSPECCIÓN Y REVISIÓN DE INSTALACIONES RECEPTORAS Y APARATOS DE GAS</x:t>
+          <x:t>ACTIVIDADES DE GESTIÓN DEL PEQUEÑO COMERCIO</x:t>
         </x:is>
       </x:c>
       <x:c r="D174" s="1" t="n">
         <x:v>46098.9583333333</x:v>
       </x:c>
       <x:c r="E174" s="2" t="n">
-        <x:v>46156.9166666667</x:v>
+        <x:v>46169.9166666667</x:v>
       </x:c>
       <x:c r="F174" t="inlineStr">
         <x:is>
@@ -5888,97 +5893,102 @@
       </x:c>
       <x:c r="G174" t="inlineStr">
         <x:is>
-          <x:t>EMPRENDE Y GESTIONA 2015, S.L.</x:t>
+          <x:t>CONECTANDO LOCAL, S.L.</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="175">
       <x:c r="A175" t="inlineStr">
         <x:is>
-          <x:t>25/5639</x:t>
+          <x:t>25/5548</x:t>
         </x:is>
       </x:c>
       <x:c r="B175" t="inlineStr">
         <x:is>
-          <x:t>COML0111</x:t>
+          <x:t>HOTI0108</x:t>
         </x:is>
       </x:c>
       <x:c r="C175" t="inlineStr">
         <x:is>
-          <x:t>TRÁFICO DE VIAJEROS POR CARRETERA</x:t>
+          <x:t>PROMOCIÓN TURÍSTICA LOCAL E INFORMACIÓN AL VISITANTE</x:t>
         </x:is>
       </x:c>
       <x:c r="D175" s="1" t="n">
         <x:v>46098.9583333333</x:v>
       </x:c>
       <x:c r="E175" s="2" t="n">
-        <x:v>46198.9166666667</x:v>
+        <x:v>46287.9166666667</x:v>
       </x:c>
       <x:c r="F175" t="inlineStr">
         <x:is>
-          <x:t>Presencial</x:t>
+          <x:t>Teleformación</x:t>
         </x:is>
       </x:c>
       <x:c r="G175" t="inlineStr">
         <x:is>
-          <x:t>CENTRO DE FORMACIÓN ZARZAQUEMADA S.L.</x:t>
+          <x:t>CONECTANDO LOCAL, S.L.</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="176">
       <x:c r="A176" t="inlineStr">
         <x:is>
-          <x:t>25/5833</x:t>
+          <x:t>25/5559</x:t>
         </x:is>
       </x:c>
       <x:c r="B176" t="inlineStr">
         <x:is>
-          <x:t>AGAJ0109</x:t>
+          <x:t>HOTR0109</x:t>
         </x:is>
       </x:c>
       <x:c r="C176" t="inlineStr">
         <x:is>
-          <x:t>GESTIÓN Y MANTENIMIENTO DE ÁRBOLES Y PALMERAS ORNAMENTALES</x:t>
+          <x:t>OPERACIONES BÁSICAS DE PASTELERÍA</x:t>
         </x:is>
       </x:c>
       <x:c r="D176" s="1" t="n">
         <x:v>46098.9583333333</x:v>
       </x:c>
       <x:c r="E176" s="2" t="n">
-        <x:v>46195.9166666667</x:v>
+        <x:v>46196.9166666667</x:v>
       </x:c>
       <x:c r="F176" t="inlineStr">
         <x:is>
-          <x:t>Presencial</x:t>
+          <x:t>Teleformación</x:t>
         </x:is>
       </x:c>
       <x:c r="G176" t="inlineStr">
         <x:is>
-          <x:t>ARACOVE</x:t>
+          <x:t>CENTRO ARANDA SCHOLA SL</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H176" t="inlineStr">
+        <x:is>
+          <x:t>MADRID</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="177">
       <x:c r="A177" t="inlineStr">
         <x:is>
-          <x:t>23/8315</x:t>
+          <x:t>25/5629</x:t>
         </x:is>
       </x:c>
       <x:c r="B177" t="inlineStr">
         <x:is>
-          <x:t>SSCI0109</x:t>
+          <x:t>ENAS0110</x:t>
         </x:is>
       </x:c>
       <x:c r="C177" t="inlineStr">
         <x:is>
-          <x:t>EMPLEO DOMÉSTICO</x:t>
+          <x:t>MONTAJE, PUESTA EN SERVICIO, MANTENIMIENTO, INSPECCIÓN Y REVISIÓN DE INSTALACIONES RECEPTORAS Y APARATOS DE GAS</x:t>
         </x:is>
       </x:c>
       <x:c r="D177" s="1" t="n">
-        <x:v>46097.9583333333</x:v>
+        <x:v>46098.9583333333</x:v>
       </x:c>
       <x:c r="E177" s="2" t="n">
-        <x:v>46132.9166666667</x:v>
+        <x:v>46156.9166666667</x:v>
       </x:c>
       <x:c r="F177" t="inlineStr">
         <x:is>
@@ -5987,31 +5997,31 @@
       </x:c>
       <x:c r="G177" t="inlineStr">
         <x:is>
-          <x:t>LOPEZ DE SANTIAGO CONSULTORES SL</x:t>
+          <x:t>EMPRENDE Y GESTIONA 2015, S.L.</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="178">
       <x:c r="A178" t="inlineStr">
         <x:is>
-          <x:t>23/8387</x:t>
+          <x:t>25/5639</x:t>
         </x:is>
       </x:c>
       <x:c r="B178" t="inlineStr">
         <x:is>
-          <x:t>SSCE0111</x:t>
+          <x:t>COML0111</x:t>
         </x:is>
       </x:c>
       <x:c r="C178" t="inlineStr">
         <x:is>
-          <x:t>PROMOCIÓN E INTERVENCIÓN SOCIOEDUCATIVA CON PERSONAS CON DISCAPACIDAD</x:t>
+          <x:t>TRÁFICO DE VIAJEROS POR CARRETERA</x:t>
         </x:is>
       </x:c>
       <x:c r="D178" s="1" t="n">
-        <x:v>46097.9583333333</x:v>
+        <x:v>46098.9583333333</x:v>
       </x:c>
       <x:c r="E178" s="2" t="n">
-        <x:v>46233.9583333333</x:v>
+        <x:v>46198.9166666667</x:v>
       </x:c>
       <x:c r="F178" t="inlineStr">
         <x:is>
@@ -6020,31 +6030,31 @@
       </x:c>
       <x:c r="G178" t="inlineStr">
         <x:is>
-          <x:t>SOLUCIONES CONSULTORAS FORMATIVAS C.C.R. SL UNIPERSONAL</x:t>
+          <x:t>CENTRO DE FORMACIÓN ZARZAQUEMADA S.L.</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="179">
       <x:c r="A179" t="inlineStr">
         <x:is>
-          <x:t>25/5093</x:t>
+          <x:t>25/5833</x:t>
         </x:is>
       </x:c>
       <x:c r="B179" t="inlineStr">
         <x:is>
-          <x:t>IFCD0210</x:t>
+          <x:t>AGAJ0109</x:t>
         </x:is>
       </x:c>
       <x:c r="C179" t="inlineStr">
         <x:is>
-          <x:t>DESARROLLO DE APLICACIONES CON TECNOLOGÍAS WEB</x:t>
+          <x:t>GESTIÓN Y MANTENIMIENTO DE ÁRBOLES Y PALMERAS ORNAMENTALES</x:t>
         </x:is>
       </x:c>
       <x:c r="D179" s="1" t="n">
-        <x:v>46097.9583333333</x:v>
+        <x:v>46098.9583333333</x:v>
       </x:c>
       <x:c r="E179" s="2" t="n">
-        <x:v>46201.9166666667</x:v>
+        <x:v>46195.9166666667</x:v>
       </x:c>
       <x:c r="F179" t="inlineStr">
         <x:is>
@@ -6053,36 +6063,31 @@
       </x:c>
       <x:c r="G179" t="inlineStr">
         <x:is>
-          <x:t>MARSDIGITAL, S.L.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H179" t="inlineStr">
-        <x:is>
-          <x:t>Madrid</x:t>
+          <x:t>ARACOVE</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="180">
       <x:c r="A180" t="inlineStr">
         <x:is>
-          <x:t>25/5491</x:t>
+          <x:t>23/8315</x:t>
         </x:is>
       </x:c>
       <x:c r="B180" t="inlineStr">
         <x:is>
-          <x:t>IMPE0108</x:t>
+          <x:t>SSCI0109</x:t>
         </x:is>
       </x:c>
       <x:c r="C180" t="inlineStr">
         <x:is>
-          <x:t>SERVICIOS AUXILIARES DE ESTÉTICA</x:t>
+          <x:t>EMPLEO DOMÉSTICO</x:t>
         </x:is>
       </x:c>
       <x:c r="D180" s="1" t="n">
         <x:v>46097.9583333333</x:v>
       </x:c>
       <x:c r="E180" s="2" t="n">
-        <x:v>46184.9166666667</x:v>
+        <x:v>46132.9166666667</x:v>
       </x:c>
       <x:c r="F180" t="inlineStr">
         <x:is>
@@ -6091,36 +6096,31 @@
       </x:c>
       <x:c r="G180" t="inlineStr">
         <x:is>
-          <x:t>FORMAJOBS S.L.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H180" t="inlineStr">
-        <x:is>
-          <x:t>Leganés</x:t>
+          <x:t>LOPEZ DE SANTIAGO CONSULTORES SL</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="181">
       <x:c r="A181" t="inlineStr">
         <x:is>
-          <x:t>25/5720</x:t>
+          <x:t>23/8387</x:t>
         </x:is>
       </x:c>
       <x:c r="B181" t="inlineStr">
         <x:is>
-          <x:t>ELEE0110</x:t>
+          <x:t>SSCE0111</x:t>
         </x:is>
       </x:c>
       <x:c r="C181" t="inlineStr">
         <x:is>
-          <x:t>DESARROLLO DE PROYECTOS DE INSTALACIONES ELÉCTRICAS EN EL ENTORNO DE EDIFICIOS Y CON FINES ESPECIALES</x:t>
+          <x:t>PROMOCIÓN E INTERVENCIÓN SOCIOEDUCATIVA CON PERSONAS CON DISCAPACIDAD</x:t>
         </x:is>
       </x:c>
       <x:c r="D181" s="1" t="n">
         <x:v>46097.9583333333</x:v>
       </x:c>
       <x:c r="E181" s="2" t="n">
-        <x:v>46212.9583333333</x:v>
+        <x:v>46233.9583333333</x:v>
       </x:c>
       <x:c r="F181" t="inlineStr">
         <x:is>
@@ -6136,19 +6136,24 @@
     <x:row r="182">
       <x:c r="A182" t="inlineStr">
         <x:is>
-          <x:t>25/9012</x:t>
+          <x:t>25/5093</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B182" t="inlineStr">
+        <x:is>
+          <x:t>IFCD0210</x:t>
         </x:is>
       </x:c>
       <x:c r="C182" t="inlineStr">
         <x:is>
-          <x:t>OPERACIONES AUXILIARES DE MANTENIMIENTO EN ELECTROMECÁNICA DE VEHÍCULOS</x:t>
+          <x:t>DESARROLLO DE APLICACIONES CON TECNOLOGÍAS WEB</x:t>
         </x:is>
       </x:c>
       <x:c r="D182" s="1" t="n">
         <x:v>46097.9583333333</x:v>
       </x:c>
       <x:c r="E182" s="2" t="n">
-        <x:v>46163.9166666667</x:v>
+        <x:v>46201.9166666667</x:v>
       </x:c>
       <x:c r="F182" t="inlineStr">
         <x:is>
@@ -6157,36 +6162,36 @@
       </x:c>
       <x:c r="G182" t="inlineStr">
         <x:is>
-          <x:t>Gala Formación CTM1</x:t>
+          <x:t>MARSDIGITAL, S.L.</x:t>
         </x:is>
       </x:c>
       <x:c r="H182" t="inlineStr">
         <x:is>
-          <x:t>MADRID</x:t>
+          <x:t>Madrid</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="183">
       <x:c r="A183" t="inlineStr">
         <x:is>
-          <x:t>25/4950</x:t>
+          <x:t>25/5491</x:t>
         </x:is>
       </x:c>
       <x:c r="B183" t="inlineStr">
         <x:is>
-          <x:t>AFDA0110</x:t>
+          <x:t>IMPE0108</x:t>
         </x:is>
       </x:c>
       <x:c r="C183" t="inlineStr">
         <x:is>
-          <x:t>ACONDICIONAMIENTO FÍSICO EN GRUPO CON SOPORTE MUSICAL</x:t>
+          <x:t>SERVICIOS AUXILIARES DE ESTÉTICA</x:t>
         </x:is>
       </x:c>
       <x:c r="D183" s="1" t="n">
-        <x:v>46096.9583333333</x:v>
+        <x:v>46097.9583333333</x:v>
       </x:c>
       <x:c r="E183" s="2" t="n">
-        <x:v>46217.9166666667</x:v>
+        <x:v>46184.9166666667</x:v>
       </x:c>
       <x:c r="F183" t="inlineStr">
         <x:is>
@@ -6195,31 +6200,36 @@
       </x:c>
       <x:c r="G183" t="inlineStr">
         <x:is>
-          <x:t>ANGEL FERNANDEZ-ROLDAN GONZALEZ</x:t>
+          <x:t>FORMAJOBS S.L.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H183" t="inlineStr">
+        <x:is>
+          <x:t>Leganés</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="184">
       <x:c r="A184" t="inlineStr">
         <x:is>
-          <x:t>25/4965</x:t>
+          <x:t>25/5720</x:t>
         </x:is>
       </x:c>
       <x:c r="B184" t="inlineStr">
         <x:is>
-          <x:t>TMVO0111</x:t>
+          <x:t>ELEE0110</x:t>
         </x:is>
       </x:c>
       <x:c r="C184" t="inlineStr">
         <x:is>
-          <x:t>TRIPULACIÓN DE CABINA DE PASAJEROS</x:t>
+          <x:t>DESARROLLO DE PROYECTOS DE INSTALACIONES ELÉCTRICAS EN EL ENTORNO DE EDIFICIOS Y CON FINES ESPECIALES</x:t>
         </x:is>
       </x:c>
       <x:c r="D184" s="1" t="n">
-        <x:v>46096.9583333333</x:v>
+        <x:v>46097.9583333333</x:v>
       </x:c>
       <x:c r="E184" s="2" t="n">
-        <x:v>46216.9166666667</x:v>
+        <x:v>46212.9583333333</x:v>
       </x:c>
       <x:c r="F184" t="inlineStr">
         <x:is>
@@ -6228,31 +6238,26 @@
       </x:c>
       <x:c r="G184" t="inlineStr">
         <x:is>
-          <x:t>BAI FORMACIÓN SA</x:t>
+          <x:t>SOLUCIONES CONSULTORAS FORMATIVAS C.C.R. SL UNIPERSONAL</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="185">
       <x:c r="A185" t="inlineStr">
         <x:is>
-          <x:t>25/5379</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B185" t="inlineStr">
-        <x:is>
-          <x:t>IFCD0210</x:t>
+          <x:t>25/9012</x:t>
         </x:is>
       </x:c>
       <x:c r="C185" t="inlineStr">
         <x:is>
-          <x:t>DESARROLLO DE APLICACIONES CON TECNOLOGÍAS WEB</x:t>
+          <x:t>OPERACIONES AUXILIARES DE MANTENIMIENTO EN ELECTROMECÁNICA DE VEHÍCULOS</x:t>
         </x:is>
       </x:c>
       <x:c r="D185" s="1" t="n">
-        <x:v>46096.9583333333</x:v>
+        <x:v>46097.9583333333</x:v>
       </x:c>
       <x:c r="E185" s="2" t="n">
-        <x:v>46230.9166666667</x:v>
+        <x:v>46163.9166666667</x:v>
       </x:c>
       <x:c r="F185" t="inlineStr">
         <x:is>
@@ -6261,31 +6266,36 @@
       </x:c>
       <x:c r="G185" t="inlineStr">
         <x:is>
-          <x:t>FORMACIÓN Y EDUCACIÓN INTEGRAL S.L.</x:t>
+          <x:t>Gala Formación CTM1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H185" t="inlineStr">
+        <x:is>
+          <x:t>MADRID</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="186">
       <x:c r="A186" t="inlineStr">
         <x:is>
-          <x:t>25/5538</x:t>
+          <x:t>25/4950</x:t>
         </x:is>
       </x:c>
       <x:c r="B186" t="inlineStr">
         <x:is>
-          <x:t>IMPE0109</x:t>
+          <x:t>AFDA0110</x:t>
         </x:is>
       </x:c>
       <x:c r="C186" t="inlineStr">
         <x:is>
-          <x:t>BRONCEADO, MAQUILLAJE Y DEPILACIÓN AVANZADA</x:t>
+          <x:t>ACONDICIONAMIENTO FÍSICO EN GRUPO CON SOPORTE MUSICAL</x:t>
         </x:is>
       </x:c>
       <x:c r="D186" s="1" t="n">
         <x:v>46096.9583333333</x:v>
       </x:c>
       <x:c r="E186" s="2" t="n">
-        <x:v>46224.9166666667</x:v>
+        <x:v>46217.9166666667</x:v>
       </x:c>
       <x:c r="F186" t="inlineStr">
         <x:is>
@@ -6294,31 +6304,31 @@
       </x:c>
       <x:c r="G186" t="inlineStr">
         <x:is>
-          <x:t>ECOLE DIMAGE TRIUNFO, S.L.</x:t>
+          <x:t>ANGEL FERNANDEZ-ROLDAN GONZALEZ</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="187">
       <x:c r="A187" t="inlineStr">
         <x:is>
-          <x:t>25/4951</x:t>
+          <x:t>25/4965</x:t>
         </x:is>
       </x:c>
       <x:c r="B187" t="inlineStr">
         <x:is>
-          <x:t>AFDA0111</x:t>
+          <x:t>TMVO0111</x:t>
         </x:is>
       </x:c>
       <x:c r="C187" t="inlineStr">
         <x:is>
-          <x:t>FITNESS ACUÁTICO E HIDROCINESIA</x:t>
+          <x:t>TRIPULACIÓN DE CABINA DE PASAJEROS</x:t>
         </x:is>
       </x:c>
       <x:c r="D187" s="1" t="n">
-        <x:v>46093.9583333333</x:v>
+        <x:v>46096.9583333333</x:v>
       </x:c>
       <x:c r="E187" s="2" t="n">
-        <x:v>46233.9166666667</x:v>
+        <x:v>46216.9166666667</x:v>
       </x:c>
       <x:c r="F187" t="inlineStr">
         <x:is>
@@ -6327,61 +6337,64 @@
       </x:c>
       <x:c r="G187" t="inlineStr">
         <x:is>
-          <x:t>ANGEL FERNANDEZ-ROLDAN GONZALEZ</x:t>
+          <x:t>BAI FORMACIÓN SA</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="188">
       <x:c r="A188" t="inlineStr">
         <x:is>
-          <x:t>25/4995</x:t>
+          <x:t>25/5379</x:t>
         </x:is>
       </x:c>
       <x:c r="B188" t="inlineStr">
         <x:is>
-          <x:t>SSCG0209</x:t>
+          <x:t>IFCD0210</x:t>
         </x:is>
       </x:c>
       <x:c r="C188" t="inlineStr">
         <x:is>
-          <x:t>MEDIACIÓN COMUNITARIA</x:t>
+          <x:t>DESARROLLO DE APLICACIONES CON TECNOLOGÍAS WEB</x:t>
         </x:is>
       </x:c>
       <x:c r="D188" s="1" t="n">
-        <x:v>46092.9583333333</x:v>
+        <x:v>46096.9583333333</x:v>
+      </x:c>
+      <x:c r="E188" s="2" t="n">
+        <x:v>46230.9166666667</x:v>
       </x:c>
       <x:c r="F188" t="inlineStr">
         <x:is>
-          <x:t>Teleformación</x:t>
+          <x:t>Presencial</x:t>
         </x:is>
       </x:c>
       <x:c r="G188" t="inlineStr">
         <x:is>
-          <x:t>CENTRO DE ESTUDIOS ADAMS EDICIONES VALBUENA, S.A.</x:t>
+          <x:t>FORMACIÓN Y EDUCACIÓN INTEGRAL S.L.</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="189">
       <x:c r="A189" t="inlineStr">
         <x:is>
-          <x:t>25/5416</x:t>
+          <x:t>25/5538</x:t>
         </x:is>
       </x:c>
       <x:c r="B189" t="inlineStr">
         <x:is>
-          <x:t>IMPE0210</x:t>
+          <x:t>IMPE0109</x:t>
         </x:is>
       </x:c>
       <x:c r="C189" t="inlineStr">
         <x:is>
-          <x:t>TRATAMIENTOS ESTÉTICOS</x:t>
+          <x:t>BRONCEADO, MAQUILLAJE Y DEPILACIÓN AVANZADA</x:t>
         </x:is>
       </x:c>
       <x:c r="D189" s="1" t="n">
-        <x:v>46092.9583333333</x:v>
+        <x:v>46096.9583333333</x:v>
       </x:c>
       <x:c r="E189" s="2" t="n">
-        <x:v>46231.9166666667</x:v>
+        <x:v>46224.9166666667</x:v>
       </x:c>
       <x:c r="F189" t="inlineStr">
         <x:is>
@@ -6390,69 +6403,61 @@
       </x:c>
       <x:c r="G189" t="inlineStr">
         <x:is>
-          <x:t>ENSEÑANZA CREATIVA DE IMAGEN PERSONALIZADA S.L.</x:t>
+          <x:t>ECOLE DIMAGE TRIUNFO, S.L.</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="190">
       <x:c r="A190" t="inlineStr">
         <x:is>
-          <x:t>25/5423</x:t>
+          <x:t>25/4995</x:t>
         </x:is>
       </x:c>
       <x:c r="B190" t="inlineStr">
         <x:is>
-          <x:t>IMSV0108</x:t>
+          <x:t>SSCG0209</x:t>
         </x:is>
       </x:c>
       <x:c r="C190" t="inlineStr">
         <x:is>
-          <x:t>ASISTENCIA A LA PRODUCCIÓN CINEMATOGRÁFICA Y DE OBRAS AUDIOVISUALES</x:t>
+          <x:t>MEDIACIÓN COMUNITARIA</x:t>
         </x:is>
       </x:c>
       <x:c r="D190" s="1" t="n">
         <x:v>46092.9583333333</x:v>
       </x:c>
-      <x:c r="E190" s="2" t="n">
-        <x:v>46203.9166666667</x:v>
-      </x:c>
       <x:c r="F190" t="inlineStr">
         <x:is>
-          <x:t>Presencial</x:t>
+          <x:t>Teleformación</x:t>
         </x:is>
       </x:c>
       <x:c r="G190" t="inlineStr">
         <x:is>
-          <x:t>TALLER CEFORA S.L.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H190" t="inlineStr">
-        <x:is>
-          <x:t>Móstoles</x:t>
+          <x:t>CENTRO DE ESTUDIOS ADAMS EDICIONES VALBUENA, S.A.</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="191">
       <x:c r="A191" t="inlineStr">
         <x:is>
-          <x:t>25/5549</x:t>
+          <x:t>25/5416</x:t>
         </x:is>
       </x:c>
       <x:c r="B191" t="inlineStr">
         <x:is>
-          <x:t>EOCB0108</x:t>
+          <x:t>IMPE0210</x:t>
         </x:is>
       </x:c>
       <x:c r="C191" t="inlineStr">
         <x:is>
-          <x:t>FÁBRICAS DE ALBAÑILERÍA</x:t>
+          <x:t>TRATAMIENTOS ESTÉTICOS</x:t>
         </x:is>
       </x:c>
       <x:c r="D191" s="1" t="n">
         <x:v>46092.9583333333</x:v>
       </x:c>
       <x:c r="E191" s="2" t="n">
-        <x:v>46177.9166666667</x:v>
+        <x:v>46231.9166666667</x:v>
       </x:c>
       <x:c r="F191" t="inlineStr">
         <x:is>
@@ -6461,26 +6466,31 @@
       </x:c>
       <x:c r="G191" t="inlineStr">
         <x:is>
-          <x:t>ADARA FORMACION, S.L.</x:t>
+          <x:t>ENSEÑANZA CREATIVA DE IMAGEN PERSONALIZADA S.L.</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="192">
       <x:c r="A192" t="inlineStr">
         <x:is>
-          <x:t>25/2395</x:t>
+          <x:t>25/5423</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B192" t="inlineStr">
+        <x:is>
+          <x:t>IMSV0108</x:t>
         </x:is>
       </x:c>
       <x:c r="C192" t="inlineStr">
         <x:is>
-          <x:t>OPERACIÓN DE REDES DEPARTAMENTALES</x:t>
+          <x:t>ASISTENCIA A LA PRODUCCIÓN CINEMATOGRÁFICA Y DE OBRAS AUDIOVISUALES</x:t>
         </x:is>
       </x:c>
       <x:c r="D192" s="1" t="n">
         <x:v>46092.9583333333</x:v>
       </x:c>
       <x:c r="E192" s="2" t="n">
-        <x:v>46212.9166666667</x:v>
+        <x:v>46203.9166666667</x:v>
       </x:c>
       <x:c r="F192" t="inlineStr">
         <x:is>
@@ -6489,31 +6499,36 @@
       </x:c>
       <x:c r="G192" t="inlineStr">
         <x:is>
-          <x:t>CENTRO DE FORMACIÓN DIGITAL SAN BLAS</x:t>
+          <x:t>TALLER CEFORA S.L.</x:t>
         </x:is>
       </x:c>
       <x:c r="H192" t="inlineStr">
         <x:is>
-          <x:t>MADRID</x:t>
+          <x:t>Móstoles</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="193">
       <x:c r="A193" t="inlineStr">
         <x:is>
-          <x:t>25/2151</x:t>
+          <x:t>25/5549</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B193" t="inlineStr">
+        <x:is>
+          <x:t>EOCB0108</x:t>
         </x:is>
       </x:c>
       <x:c r="C193" t="inlineStr">
         <x:is>
-          <x:t>DESARROLLO DE APLICACIONES CON TECNOLOGÍA WEB</x:t>
+          <x:t>FÁBRICAS DE ALBAÑILERÍA</x:t>
         </x:is>
       </x:c>
       <x:c r="D193" s="1" t="n">
-        <x:v>46091.9583333333</x:v>
+        <x:v>46092.9583333333</x:v>
       </x:c>
       <x:c r="E193" s="2" t="n">
-        <x:v>46197.9166666667</x:v>
+        <x:v>46177.9166666667</x:v>
       </x:c>
       <x:c r="F193" t="inlineStr">
         <x:is>
@@ -6522,31 +6537,26 @@
       </x:c>
       <x:c r="G193" t="inlineStr">
         <x:is>
-          <x:t>CENTRO DE FORMACIÓN DIGITAL ALCOBENDAS</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H193" t="inlineStr">
-        <x:is>
-          <x:t>ALCOBENDAS</x:t>
+          <x:t>ADARA FORMACION, S.L.</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="194">
       <x:c r="A194" t="inlineStr">
         <x:is>
-          <x:t>25/2152</x:t>
+          <x:t>25/2395</x:t>
         </x:is>
       </x:c>
       <x:c r="C194" t="inlineStr">
         <x:is>
-          <x:t>DESARROLLO DE APLICACIONES CON TECNOLOGÍA WEB</x:t>
+          <x:t>OPERACIÓN DE REDES DEPARTAMENTALES</x:t>
         </x:is>
       </x:c>
       <x:c r="D194" s="1" t="n">
-        <x:v>46091.9583333333</x:v>
+        <x:v>46092.9583333333</x:v>
       </x:c>
       <x:c r="E194" s="2" t="n">
-        <x:v>46139.9166666667</x:v>
+        <x:v>46212.9166666667</x:v>
       </x:c>
       <x:c r="F194" t="inlineStr">
         <x:is>
@@ -6555,34 +6565,32 @@
       </x:c>
       <x:c r="G194" t="inlineStr">
         <x:is>
-          <x:t>CENTRO DE FORMACIÓN DIGITAL ALCOBENDAS</x:t>
+          <x:t>CENTRO DE FORMACIÓN DIGITAL SAN BLAS</x:t>
         </x:is>
       </x:c>
       <x:c r="H194" t="inlineStr">
         <x:is>
-          <x:t>ALCOBENDAS</x:t>
+          <x:t>MADRID</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="195">
       <x:c r="A195" t="inlineStr">
         <x:is>
-          <x:t>25/4974</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B195" t="inlineStr">
-        <x:is>
-          <x:t>ADGG0108</x:t>
+          <x:t>25/2151</x:t>
         </x:is>
       </x:c>
       <x:c r="C195" t="inlineStr">
         <x:is>
-          <x:t>ASISTENCIA A LA DIRECCIÓN</x:t>
+          <x:t>DESARROLLO DE APLICACIONES CON TECNOLOGÍA WEB</x:t>
         </x:is>
       </x:c>
       <x:c r="D195" s="1" t="n">
         <x:v>46091.9583333333</x:v>
       </x:c>
+      <x:c r="E195" s="2" t="n">
+        <x:v>46197.9166666667</x:v>
+      </x:c>
       <x:c r="F195" t="inlineStr">
         <x:is>
           <x:t>Presencial</x:t>
@@ -6590,31 +6598,31 @@
       </x:c>
       <x:c r="G195" t="inlineStr">
         <x:is>
-          <x:t>CENTRO DE ESTUDIOS VELAZQUEZ S.A.</x:t>
+          <x:t>CENTRO DE FORMACIÓN DIGITAL ALCOBENDAS</x:t>
         </x:is>
       </x:c>
       <x:c r="H195" t="inlineStr">
         <x:is>
-          <x:t>Madrid</x:t>
+          <x:t>ALCOBENDAS</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="196">
       <x:c r="A196" t="inlineStr">
         <x:is>
-          <x:t>25/9013</x:t>
+          <x:t>25/2152</x:t>
         </x:is>
       </x:c>
       <x:c r="C196" t="inlineStr">
         <x:is>
-          <x:t>ACTIVIDADES ADMINISTRATIVAS EN LA RELACIÓN CON EL CLIENTE</x:t>
+          <x:t>DESARROLLO DE APLICACIONES CON TECNOLOGÍA WEB</x:t>
         </x:is>
       </x:c>
       <x:c r="D196" s="1" t="n">
         <x:v>46091.9583333333</x:v>
       </x:c>
       <x:c r="E196" s="2" t="n">
-        <x:v>46278.9166666667</x:v>
+        <x:v>46139.9166666667</x:v>
       </x:c>
       <x:c r="F196" t="inlineStr">
         <x:is>
@@ -6623,32 +6631,34 @@
       </x:c>
       <x:c r="G196" t="inlineStr">
         <x:is>
-          <x:t>PLATO SUR</x:t>
+          <x:t>CENTRO DE FORMACIÓN DIGITAL ALCOBENDAS</x:t>
         </x:is>
       </x:c>
       <x:c r="H196" t="inlineStr">
         <x:is>
-          <x:t>LEGANES</x:t>
+          <x:t>ALCOBENDAS</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="197">
       <x:c r="A197" t="inlineStr">
         <x:is>
-          <x:t>25/2361</x:t>
+          <x:t>25/4974</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B197" t="inlineStr">
+        <x:is>
+          <x:t>ADGG0108</x:t>
         </x:is>
       </x:c>
       <x:c r="C197" t="inlineStr">
         <x:is>
-          <x:t>IMPLANTACIÓN Y GESTIÓN DE ELEMENTOS INFORMÁTICOS - SISTEMAS DOMÓTICOS E INMÓTICOS</x:t>
+          <x:t>ASISTENCIA A LA DIRECCIÓN</x:t>
         </x:is>
       </x:c>
       <x:c r="D197" s="1" t="n">
         <x:v>46091.9583333333</x:v>
       </x:c>
-      <x:c r="E197" s="2" t="n">
-        <x:v>46215.9166666667</x:v>
-      </x:c>
       <x:c r="F197" t="inlineStr">
         <x:is>
           <x:t>Presencial</x:t>
@@ -6656,36 +6666,31 @@
       </x:c>
       <x:c r="G197" t="inlineStr">
         <x:is>
-          <x:t>CENTRO DE FORMACIÓN DIGITAL SAN BLAS</x:t>
+          <x:t>CENTRO DE ESTUDIOS VELAZQUEZ S.A.</x:t>
         </x:is>
       </x:c>
       <x:c r="H197" t="inlineStr">
         <x:is>
-          <x:t>MADRID</x:t>
+          <x:t>Madrid</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="198">
       <x:c r="A198" t="inlineStr">
         <x:is>
-          <x:t>23/8388</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B198" t="inlineStr">
-        <x:is>
-          <x:t>SSCG0209</x:t>
+          <x:t>25/9013</x:t>
         </x:is>
       </x:c>
       <x:c r="C198" t="inlineStr">
         <x:is>
-          <x:t>MEDIACIÓN COMUNITARIA</x:t>
+          <x:t>ACTIVIDADES ADMINISTRATIVAS EN LA RELACIÓN CON EL CLIENTE</x:t>
         </x:is>
       </x:c>
       <x:c r="D198" s="1" t="n">
-        <x:v>46090.9583333333</x:v>
+        <x:v>46091.9583333333</x:v>
       </x:c>
       <x:c r="E198" s="2" t="n">
-        <x:v>46198.9583333333</x:v>
+        <x:v>46278.9166666667</x:v>
       </x:c>
       <x:c r="F198" t="inlineStr">
         <x:is>
@@ -6694,26 +6699,31 @@
       </x:c>
       <x:c r="G198" t="inlineStr">
         <x:is>
-          <x:t>SOLUCIONES CONSULTORAS FORMATIVAS C.C.R. SL UNIPERSONAL</x:t>
+          <x:t>PLATO SUR</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H198" t="inlineStr">
+        <x:is>
+          <x:t>LEGANES</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="199">
       <x:c r="A199" t="inlineStr">
         <x:is>
-          <x:t>25/2149</x:t>
+          <x:t>25/2361</x:t>
         </x:is>
       </x:c>
       <x:c r="C199" t="inlineStr">
         <x:is>
-          <x:t>CONFECCIÓN Y PUBLICACIÓN DE PÁGINAS WEB</x:t>
+          <x:t>IMPLANTACIÓN Y GESTIÓN DE ELEMENTOS INFORMÁTICOS - SISTEMAS DOMÓTICOS E INMÓTICOS</x:t>
         </x:is>
       </x:c>
       <x:c r="D199" s="1" t="n">
-        <x:v>46090.9583333333</x:v>
+        <x:v>46091.9583333333</x:v>
       </x:c>
       <x:c r="E199" s="2" t="n">
-        <x:v>46124.9166666667</x:v>
+        <x:v>46215.9166666667</x:v>
       </x:c>
       <x:c r="F199" t="inlineStr">
         <x:is>
@@ -6722,31 +6732,36 @@
       </x:c>
       <x:c r="G199" t="inlineStr">
         <x:is>
-          <x:t>CENTRO DE FORMACIÓN DIGITAL ALCOBENDAS</x:t>
+          <x:t>CENTRO DE FORMACIÓN DIGITAL SAN BLAS</x:t>
         </x:is>
       </x:c>
       <x:c r="H199" t="inlineStr">
         <x:is>
-          <x:t>ALCOBENDAS</x:t>
+          <x:t>MADRID</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="200">
       <x:c r="A200" t="inlineStr">
         <x:is>
-          <x:t>25/2150</x:t>
+          <x:t>23/8388</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B200" t="inlineStr">
+        <x:is>
+          <x:t>SSCG0209</x:t>
         </x:is>
       </x:c>
       <x:c r="C200" t="inlineStr">
         <x:is>
-          <x:t>CONFECCIÓN Y PUBLICACIÓN DE PÁGINAS WEB</x:t>
+          <x:t>MEDIACIÓN COMUNITARIA</x:t>
         </x:is>
       </x:c>
       <x:c r="D200" s="1" t="n">
         <x:v>46090.9583333333</x:v>
       </x:c>
       <x:c r="E200" s="2" t="n">
-        <x:v>46140.9166666667</x:v>
+        <x:v>46198.9583333333</x:v>
       </x:c>
       <x:c r="F200" t="inlineStr">
         <x:is>
@@ -6755,36 +6770,26 @@
       </x:c>
       <x:c r="G200" t="inlineStr">
         <x:is>
-          <x:t>CENTRO DE FORMACIÓN DIGITAL ALCOBENDAS</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H200" t="inlineStr">
-        <x:is>
-          <x:t>ALCOBENDAS</x:t>
+          <x:t>SOLUCIONES CONSULTORAS FORMATIVAS C.C.R. SL UNIPERSONAL</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="201">
       <x:c r="A201" t="inlineStr">
         <x:is>
-          <x:t>25/5354</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B201" t="inlineStr">
-        <x:is>
-          <x:t>IMAQ0210</x:t>
+          <x:t>25/2149</x:t>
         </x:is>
       </x:c>
       <x:c r="C201" t="inlineStr">
         <x:is>
-          <x:t>DESARROLLO DE PROYECTOS DE INSTALACIONES DE MANUTENCIÓN, ELEVACIÓN Y TRANSPORTE</x:t>
+          <x:t>CONFECCIÓN Y PUBLICACIÓN DE PÁGINAS WEB</x:t>
         </x:is>
       </x:c>
       <x:c r="D201" s="1" t="n">
         <x:v>46090.9583333333</x:v>
       </x:c>
       <x:c r="E201" s="2" t="n">
-        <x:v>46233.9166666667</x:v>
+        <x:v>46124.9166666667</x:v>
       </x:c>
       <x:c r="F201" t="inlineStr">
         <x:is>
@@ -6793,34 +6798,32 @@
       </x:c>
       <x:c r="G201" t="inlineStr">
         <x:is>
-          <x:t>LONDON EDUCATION CENTER S.L.</x:t>
+          <x:t>CENTRO DE FORMACIÓN DIGITAL ALCOBENDAS</x:t>
         </x:is>
       </x:c>
       <x:c r="H201" t="inlineStr">
         <x:is>
-          <x:t>Fuenlabrada</x:t>
+          <x:t>ALCOBENDAS</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="202">
       <x:c r="A202" t="inlineStr">
         <x:is>
-          <x:t>25/5360</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B202" t="inlineStr">
-        <x:is>
-          <x:t>ELES0110</x:t>
+          <x:t>25/2150</x:t>
         </x:is>
       </x:c>
       <x:c r="C202" t="inlineStr">
         <x:is>
-          <x:t>DESARROLLO DE PROYECTOS DE INFRAESTRUCTURAS DE TELECOMUNICACIÓN Y DE REDES DE VOZ Y DATOS EN EL ENTORNO DE EDIFICIOS</x:t>
+          <x:t>CONFECCIÓN Y PUBLICACIÓN DE PÁGINAS WEB</x:t>
         </x:is>
       </x:c>
       <x:c r="D202" s="1" t="n">
         <x:v>46090.9583333333</x:v>
       </x:c>
+      <x:c r="E202" s="2" t="n">
+        <x:v>46140.9166666667</x:v>
+      </x:c>
       <x:c r="F202" t="inlineStr">
         <x:is>
           <x:t>Presencial</x:t>
@@ -6828,70 +6831,72 @@
       </x:c>
       <x:c r="G202" t="inlineStr">
         <x:is>
-          <x:t>SERPROFES SL</x:t>
+          <x:t>CENTRO DE FORMACIÓN DIGITAL ALCOBENDAS</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H202" t="inlineStr">
+        <x:is>
+          <x:t>ALCOBENDAS</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="203">
       <x:c r="A203" t="inlineStr">
         <x:is>
-          <x:t>25/5560</x:t>
+          <x:t>25/5354</x:t>
         </x:is>
       </x:c>
       <x:c r="B203" t="inlineStr">
         <x:is>
-          <x:t>HOTR0109</x:t>
+          <x:t>IMAQ0210</x:t>
         </x:is>
       </x:c>
       <x:c r="C203" t="inlineStr">
         <x:is>
-          <x:t>OPERACIONES BÁSICAS DE PASTELERÍA</x:t>
+          <x:t>DESARROLLO DE PROYECTOS DE INSTALACIONES DE MANUTENCIÓN, ELEVACIÓN Y TRANSPORTE</x:t>
         </x:is>
       </x:c>
       <x:c r="D203" s="1" t="n">
         <x:v>46090.9583333333</x:v>
       </x:c>
       <x:c r="E203" s="2" t="n">
-        <x:v>46190.9166666667</x:v>
+        <x:v>46233.9166666667</x:v>
       </x:c>
       <x:c r="F203" t="inlineStr">
         <x:is>
-          <x:t>Teleformación</x:t>
+          <x:t>Presencial</x:t>
         </x:is>
       </x:c>
       <x:c r="G203" t="inlineStr">
         <x:is>
-          <x:t>CENTRO ARANDA SCHOLA SL</x:t>
+          <x:t>LONDON EDUCATION CENTER S.L.</x:t>
         </x:is>
       </x:c>
       <x:c r="H203" t="inlineStr">
         <x:is>
-          <x:t>MADRID</x:t>
+          <x:t>Fuenlabrada</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="204">
       <x:c r="A204" t="inlineStr">
         <x:is>
-          <x:t>25/5631</x:t>
+          <x:t>25/5360</x:t>
         </x:is>
       </x:c>
       <x:c r="B204" t="inlineStr">
         <x:is>
-          <x:t>IMSV0108</x:t>
+          <x:t>ELES0110</x:t>
         </x:is>
       </x:c>
       <x:c r="C204" t="inlineStr">
         <x:is>
-          <x:t>ASISTENCIA A LA PRODUCCIÓN CINEMATOGRÁFICA Y DE OBRAS AUDIOVISUALES</x:t>
+          <x:t>DESARROLLO DE PROYECTOS DE INFRAESTRUCTURAS DE TELECOMUNICACIÓN Y DE REDES DE VOZ Y DATOS EN EL ENTORNO DE EDIFICIOS</x:t>
         </x:is>
       </x:c>
       <x:c r="D204" s="1" t="n">
         <x:v>46090.9583333333</x:v>
       </x:c>
-      <x:c r="E204" s="2" t="n">
-        <x:v>46201.9166666667</x:v>
-      </x:c>
       <x:c r="F204" t="inlineStr">
         <x:is>
           <x:t>Presencial</x:t>
@@ -6899,64 +6904,69 @@
       </x:c>
       <x:c r="G204" t="inlineStr">
         <x:is>
-          <x:t>EMPRENDE Y GESTIONA 2015, S.L.</x:t>
+          <x:t>SERPROFES SL</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="205">
       <x:c r="A205" t="inlineStr">
         <x:is>
-          <x:t>25/5876</x:t>
+          <x:t>25/5560</x:t>
         </x:is>
       </x:c>
       <x:c r="B205" t="inlineStr">
         <x:is>
-          <x:t>SANT0208</x:t>
+          <x:t>HOTR0109</x:t>
         </x:is>
       </x:c>
       <x:c r="C205" t="inlineStr">
         <x:is>
-          <x:t>TRANSPORTE SANITARIO</x:t>
+          <x:t>OPERACIONES BÁSICAS DE PASTELERÍA</x:t>
         </x:is>
       </x:c>
       <x:c r="D205" s="1" t="n">
         <x:v>46090.9583333333</x:v>
       </x:c>
       <x:c r="E205" s="2" t="n">
-        <x:v>46294.9166666667</x:v>
+        <x:v>46190.9166666667</x:v>
       </x:c>
       <x:c r="F205" t="inlineStr">
         <x:is>
-          <x:t>Presencial</x:t>
+          <x:t>Teleformación</x:t>
         </x:is>
       </x:c>
       <x:c r="G205" t="inlineStr">
         <x:is>
-          <x:t>CRUZ ROJA ESPAÑOLA</x:t>
+          <x:t>CENTRO ARANDA SCHOLA SL</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H205" t="inlineStr">
+        <x:is>
+          <x:t>MADRID</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="206">
       <x:c r="A206" t="inlineStr">
         <x:is>
-          <x:t>25/8144</x:t>
+          <x:t>25/5631</x:t>
         </x:is>
       </x:c>
       <x:c r="B206" t="inlineStr">
         <x:is>
-          <x:t>ADGD0108</x:t>
+          <x:t>IMSV0108</x:t>
         </x:is>
       </x:c>
       <x:c r="C206" t="inlineStr">
         <x:is>
-          <x:t>GESTIÓN CONTABLE Y GESTIÓN ADMINISTRATIVA PARA AUDITORÍA</x:t>
+          <x:t>ASISTENCIA A LA PRODUCCIÓN CINEMATOGRÁFICA Y DE OBRAS AUDIOVISUALES</x:t>
         </x:is>
       </x:c>
       <x:c r="D206" s="1" t="n">
         <x:v>46090.9583333333</x:v>
       </x:c>
       <x:c r="E206" s="2" t="n">
-        <x:v>46210.9166666667</x:v>
+        <x:v>46201.9166666667</x:v>
       </x:c>
       <x:c r="F206" t="inlineStr">
         <x:is>
@@ -6965,26 +6975,31 @@
       </x:c>
       <x:c r="G206" t="inlineStr">
         <x:is>
-          <x:t>AYUNTAMIENTO DE SAN FERNANDO DE HENARES</x:t>
+          <x:t>EMPRENDE Y GESTIONA 2015, S.L.</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="207">
       <x:c r="A207" t="inlineStr">
         <x:is>
-          <x:t>25/9016</x:t>
+          <x:t>25/8144</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B207" t="inlineStr">
+        <x:is>
+          <x:t>ADGD0108</x:t>
         </x:is>
       </x:c>
       <x:c r="C207" t="inlineStr">
         <x:is>
-          <x:t>ACTIVIDADES ADMINISTRATIVAS EN LA RELACIÓN CON EL CLIENTE</x:t>
+          <x:t>GESTIÓN CONTABLE Y GESTIÓN ADMINISTRATIVA PARA AUDITORÍA</x:t>
         </x:is>
       </x:c>
       <x:c r="D207" s="1" t="n">
         <x:v>46090.9583333333</x:v>
       </x:c>
       <x:c r="E207" s="2" t="n">
-        <x:v>46287.9166666667</x:v>
+        <x:v>46210.9166666667</x:v>
       </x:c>
       <x:c r="F207" t="inlineStr">
         <x:is>
@@ -6993,31 +7008,26 @@
       </x:c>
       <x:c r="G207" t="inlineStr">
         <x:is>
-          <x:t>CEFORA S.L.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H207" t="inlineStr">
-        <x:is>
-          <x:t>MOSTOLES</x:t>
+          <x:t>AYUNTAMIENTO DE SAN FERNANDO DE HENARES</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="208">
       <x:c r="A208" t="inlineStr">
         <x:is>
-          <x:t>25/9022</x:t>
+          <x:t>25/9016</x:t>
         </x:is>
       </x:c>
       <x:c r="C208" t="inlineStr">
         <x:is>
-          <x:t>GESTIÓN CONTABLE, FINANCIERA Y FISCAL</x:t>
+          <x:t>ACTIVIDADES ADMINISTRATIVAS EN LA RELACIÓN CON EL CLIENTE</x:t>
         </x:is>
       </x:c>
       <x:c r="D208" s="1" t="n">
         <x:v>46090.9583333333</x:v>
       </x:c>
       <x:c r="E208" s="2" t="n">
-        <x:v>46232.9166666667</x:v>
+        <x:v>46287.9166666667</x:v>
       </x:c>
       <x:c r="F208" t="inlineStr">
         <x:is>
@@ -7026,31 +7036,31 @@
       </x:c>
       <x:c r="G208" t="inlineStr">
         <x:is>
-          <x:t>CENES</x:t>
+          <x:t>CEFORA S.L.</x:t>
         </x:is>
       </x:c>
       <x:c r="H208" t="inlineStr">
         <x:is>
-          <x:t>GETAFE</x:t>
+          <x:t>MOSTOLES</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="209">
       <x:c r="A209" t="inlineStr">
         <x:is>
-          <x:t>25/2331</x:t>
+          <x:t>25/9022</x:t>
         </x:is>
       </x:c>
       <x:c r="C209" t="inlineStr">
         <x:is>
-          <x:t>CONFECCIÓN Y PUBLICACIÓN DE PÁGINAS WEB</x:t>
+          <x:t>GESTIÓN CONTABLE, FINANCIERA Y FISCAL</x:t>
         </x:is>
       </x:c>
       <x:c r="D209" s="1" t="n">
         <x:v>46090.9583333333</x:v>
       </x:c>
       <x:c r="E209" s="2" t="n">
-        <x:v>46216.9166666667</x:v>
+        <x:v>46232.9166666667</x:v>
       </x:c>
       <x:c r="F209" t="inlineStr">
         <x:is>
@@ -7059,31 +7069,31 @@
       </x:c>
       <x:c r="G209" t="inlineStr">
         <x:is>
-          <x:t>CENTRO DE FORMACIÓN DIGITAL SAN BLAS</x:t>
+          <x:t>CENES</x:t>
         </x:is>
       </x:c>
       <x:c r="H209" t="inlineStr">
         <x:is>
-          <x:t>MADRID</x:t>
+          <x:t>GETAFE</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="210">
       <x:c r="A210" t="inlineStr">
         <x:is>
-          <x:t>25/2334</x:t>
+          <x:t>25/2331</x:t>
         </x:is>
       </x:c>
       <x:c r="C210" t="inlineStr">
         <x:is>
-          <x:t>DESARROLLO DE APLICACIONES CON TECNOLOGÍA WEB</x:t>
+          <x:t>CONFECCIÓN Y PUBLICACIÓN DE PÁGINAS WEB</x:t>
         </x:is>
       </x:c>
       <x:c r="D210" s="1" t="n">
         <x:v>46090.9583333333</x:v>
       </x:c>
       <x:c r="E210" s="2" t="n">
-        <x:v>46223.9166666667</x:v>
+        <x:v>46216.9166666667</x:v>
       </x:c>
       <x:c r="F210" t="inlineStr">
         <x:is>
@@ -7104,19 +7114,19 @@
     <x:row r="211">
       <x:c r="A211" t="inlineStr">
         <x:is>
-          <x:t>25/2388</x:t>
+          <x:t>25/2334</x:t>
         </x:is>
       </x:c>
       <x:c r="C211" t="inlineStr">
         <x:is>
-          <x:t>MONTAJE Y MANTENIMIENTO DE INFRAESTRUCTURAS DE TELECOMUNICACIONES EN EDIFICIOS</x:t>
+          <x:t>DESARROLLO DE APLICACIONES CON TECNOLOGÍA WEB</x:t>
         </x:is>
       </x:c>
       <x:c r="D211" s="1" t="n">
         <x:v>46090.9583333333</x:v>
       </x:c>
       <x:c r="E211" s="2" t="n">
-        <x:v>46194.9166666667</x:v>
+        <x:v>46223.9166666667</x:v>
       </x:c>
       <x:c r="F211" t="inlineStr">
         <x:is>
@@ -7137,19 +7147,19 @@
     <x:row r="212">
       <x:c r="A212" t="inlineStr">
         <x:is>
-          <x:t>25/2422</x:t>
+          <x:t>25/2388</x:t>
         </x:is>
       </x:c>
       <x:c r="C212" t="inlineStr">
         <x:is>
-          <x:t>OPERACIONES AUXILIARES DE MONTAJE Y MANTENIMIENTO DE EQUIPOS ELÉCTRICOS Y ELECTRÓNICOS *</x:t>
+          <x:t>MONTAJE Y MANTENIMIENTO DE INFRAESTRUCTURAS DE TELECOMUNICACIONES EN EDIFICIOS</x:t>
         </x:is>
       </x:c>
       <x:c r="D212" s="1" t="n">
         <x:v>46090.9583333333</x:v>
       </x:c>
       <x:c r="E212" s="2" t="n">
-        <x:v>46187.9166666667</x:v>
+        <x:v>46194.9166666667</x:v>
       </x:c>
       <x:c r="F212" t="inlineStr">
         <x:is>
@@ -7170,24 +7180,19 @@
     <x:row r="213">
       <x:c r="A213" t="inlineStr">
         <x:is>
-          <x:t>23/8204</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B213" t="inlineStr">
-        <x:is>
-          <x:t>IFCT0510</x:t>
+          <x:t>25/2422</x:t>
         </x:is>
       </x:c>
       <x:c r="C213" t="inlineStr">
         <x:is>
-          <x:t>GESTIÓN DE SISTEMAS INFORMÁTICOS</x:t>
+          <x:t>OPERACIONES AUXILIARES DE MONTAJE Y MANTENIMIENTO DE EQUIPOS ELÉCTRICOS Y ELECTRÓNICOS *</x:t>
         </x:is>
       </x:c>
       <x:c r="D213" s="1" t="n">
-        <x:v>46089.9583333333</x:v>
+        <x:v>46090.9583333333</x:v>
       </x:c>
       <x:c r="E213" s="2" t="n">
-        <x:v>46183.9166666667</x:v>
+        <x:v>46187.9166666667</x:v>
       </x:c>
       <x:c r="F213" t="inlineStr">
         <x:is>
@@ -7196,26 +7201,36 @@
       </x:c>
       <x:c r="G213" t="inlineStr">
         <x:is>
-          <x:t>FORMACIÓN Y EDUCACIÓN INTEGRAL S.L.</x:t>
+          <x:t>CENTRO DE FORMACIÓN DIGITAL SAN BLAS</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H213" t="inlineStr">
+        <x:is>
+          <x:t>MADRID</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="214">
       <x:c r="A214" t="inlineStr">
         <x:is>
-          <x:t>25/2148</x:t>
+          <x:t>23/8204</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B214" t="inlineStr">
+        <x:is>
+          <x:t>IFCT0510</x:t>
         </x:is>
       </x:c>
       <x:c r="C214" t="inlineStr">
         <x:is>
-          <x:t>CONFECCIÓN Y PUBLICACIÓN DE PÁGINAS WEB</x:t>
+          <x:t>GESTIÓN DE SISTEMAS INFORMÁTICOS</x:t>
         </x:is>
       </x:c>
       <x:c r="D214" s="1" t="n">
         <x:v>46089.9583333333</x:v>
       </x:c>
       <x:c r="E214" s="2" t="n">
-        <x:v>46181.9166666667</x:v>
+        <x:v>46183.9166666667</x:v>
       </x:c>
       <x:c r="F214" t="inlineStr">
         <x:is>
@@ -7224,36 +7239,26 @@
       </x:c>
       <x:c r="G214" t="inlineStr">
         <x:is>
-          <x:t>CENTRO DE FORMACIÓN DIGITAL ALCOBENDAS</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H214" t="inlineStr">
-        <x:is>
-          <x:t>ALCOBENDAS</x:t>
+          <x:t>FORMACIÓN Y EDUCACIÓN INTEGRAL S.L.</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="215">
       <x:c r="A215" t="inlineStr">
         <x:is>
-          <x:t>25/5419</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B215" t="inlineStr">
-        <x:is>
-          <x:t>IMPQ0109</x:t>
+          <x:t>25/2148</x:t>
         </x:is>
       </x:c>
       <x:c r="C215" t="inlineStr">
         <x:is>
-          <x:t>PELUQUERÍA TÉCNICO-ARTÍSTICA</x:t>
+          <x:t>CONFECCIÓN Y PUBLICACIÓN DE PÁGINAS WEB</x:t>
         </x:is>
       </x:c>
       <x:c r="D215" s="1" t="n">
         <x:v>46089.9583333333</x:v>
       </x:c>
       <x:c r="E215" s="2" t="n">
-        <x:v>46232.9166666667</x:v>
+        <x:v>46181.9166666667</x:v>
       </x:c>
       <x:c r="F215" t="inlineStr">
         <x:is>
@@ -7262,31 +7267,36 @@
       </x:c>
       <x:c r="G215" t="inlineStr">
         <x:is>
-          <x:t>ENSEÑANZA CREATIVA DE IMAGEN PERSONALIZADA S.L.</x:t>
+          <x:t>CENTRO DE FORMACIÓN DIGITAL ALCOBENDAS</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H215" t="inlineStr">
+        <x:is>
+          <x:t>ALCOBENDAS</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="216">
       <x:c r="A216" t="inlineStr">
         <x:is>
-          <x:t>25/5539</x:t>
+          <x:t>25/5419</x:t>
         </x:is>
       </x:c>
       <x:c r="B216" t="inlineStr">
         <x:is>
-          <x:t>IMPE0209</x:t>
+          <x:t>IMPQ0109</x:t>
         </x:is>
       </x:c>
       <x:c r="C216" t="inlineStr">
         <x:is>
-          <x:t>MAQUILLAJE INTEGRAL</x:t>
+          <x:t>PELUQUERÍA TÉCNICO-ARTÍSTICA</x:t>
         </x:is>
       </x:c>
       <x:c r="D216" s="1" t="n">
         <x:v>46089.9583333333</x:v>
       </x:c>
       <x:c r="E216" s="2" t="n">
-        <x:v>46225.9166666667</x:v>
+        <x:v>46232.9166666667</x:v>
       </x:c>
       <x:c r="F216" t="inlineStr">
         <x:is>
@@ -7295,26 +7305,31 @@
       </x:c>
       <x:c r="G216" t="inlineStr">
         <x:is>
-          <x:t>ECOLE DIMAGE TRIUNFO, S.L.</x:t>
+          <x:t>ENSEÑANZA CREATIVA DE IMAGEN PERSONALIZADA S.L.</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="217">
       <x:c r="A217" t="inlineStr">
         <x:is>
-          <x:t>25/5656</x:t>
+          <x:t>25/5539</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B217" t="inlineStr">
+        <x:is>
+          <x:t>IMPE0209</x:t>
         </x:is>
       </x:c>
       <x:c r="C217" t="inlineStr">
         <x:is>
-          <x:t>ARREGLOS Y ADAPTACIONES DE PRENDAS Y ARTÍCULOS EN TEXTIL Y PIEL</x:t>
+          <x:t>MAQUILLAJE INTEGRAL</x:t>
         </x:is>
       </x:c>
       <x:c r="D217" s="1" t="n">
         <x:v>46089.9583333333</x:v>
       </x:c>
       <x:c r="E217" s="2" t="n">
-        <x:v>46148.9166666667</x:v>
+        <x:v>46225.9166666667</x:v>
       </x:c>
       <x:c r="F217" t="inlineStr">
         <x:is>
@@ -7323,36 +7338,26 @@
       </x:c>
       <x:c r="G217" t="inlineStr">
         <x:is>
-          <x:t>FORMACION INTERNACIONAL VOCACIONAL Y EMPRENDIMIENTO, S.L.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H217" t="inlineStr">
-        <x:is>
-          <x:t>Alcala de Henares</x:t>
+          <x:t>ECOLE DIMAGE TRIUNFO, S.L.</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="218">
       <x:c r="A218" t="inlineStr">
         <x:is>
-          <x:t>25/5830</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B218" t="inlineStr">
-        <x:is>
-          <x:t>IMPE0209</x:t>
+          <x:t>25/5656</x:t>
         </x:is>
       </x:c>
       <x:c r="C218" t="inlineStr">
         <x:is>
-          <x:t>MAQUILLAJE INTEGRAL</x:t>
+          <x:t>ARREGLOS Y ADAPTACIONES DE PRENDAS Y ARTÍCULOS EN TEXTIL Y PIEL</x:t>
         </x:is>
       </x:c>
       <x:c r="D218" s="1" t="n">
         <x:v>46089.9583333333</x:v>
       </x:c>
       <x:c r="E218" s="2" t="n">
-        <x:v>46231.9166666667</x:v>
+        <x:v>46148.9166666667</x:v>
       </x:c>
       <x:c r="F218" t="inlineStr">
         <x:is>
@@ -7361,31 +7366,36 @@
       </x:c>
       <x:c r="G218" t="inlineStr">
         <x:is>
-          <x:t>ASOCIACION AREA DE FORMACION</x:t>
+          <x:t>FORMACION INTERNACIONAL VOCACIONAL Y EMPRENDIMIENTO, S.L.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H218" t="inlineStr">
+        <x:is>
+          <x:t>Alcala de Henares</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="219">
       <x:c r="A219" t="inlineStr">
         <x:is>
-          <x:t>25/5875</x:t>
+          <x:t>25/5830</x:t>
         </x:is>
       </x:c>
       <x:c r="B219" t="inlineStr">
         <x:is>
-          <x:t>AFDP0109</x:t>
+          <x:t>IMPE0209</x:t>
         </x:is>
       </x:c>
       <x:c r="C219" t="inlineStr">
         <x:is>
-          <x:t>SOCORRISMO EN INSTALACIONES ACUÁTICAS</x:t>
+          <x:t>MAQUILLAJE INTEGRAL</x:t>
         </x:is>
       </x:c>
       <x:c r="D219" s="1" t="n">
         <x:v>46089.9583333333</x:v>
       </x:c>
       <x:c r="E219" s="2" t="n">
-        <x:v>46187.9166666667</x:v>
+        <x:v>46231.9166666667</x:v>
       </x:c>
       <x:c r="F219" t="inlineStr">
         <x:is>
@@ -7394,31 +7404,31 @@
       </x:c>
       <x:c r="G219" t="inlineStr">
         <x:is>
-          <x:t>CRUZ ROJA ESPAÑOLA</x:t>
+          <x:t>ASOCIACION AREA DE FORMACION</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="220">
       <x:c r="A220" t="inlineStr">
         <x:is>
-          <x:t>25/5877</x:t>
+          <x:t>25/5875</x:t>
         </x:is>
       </x:c>
       <x:c r="B220" t="inlineStr">
         <x:is>
-          <x:t>SSCB0209</x:t>
+          <x:t>AFDP0109</x:t>
         </x:is>
       </x:c>
       <x:c r="C220" t="inlineStr">
         <x:is>
-          <x:t>DINAMIZACIÓN DE ACTIVIDADES DE TIEMPO LIBRE EDUCATIVO INFANTIL Y JUVENIL</x:t>
+          <x:t>SOCORRISMO EN INSTALACIONES ACUÁTICAS</x:t>
         </x:is>
       </x:c>
       <x:c r="D220" s="1" t="n">
         <x:v>46089.9583333333</x:v>
       </x:c>
       <x:c r="E220" s="2" t="n">
-        <x:v>46233.9166666667</x:v>
+        <x:v>46187.9166666667</x:v>
       </x:c>
       <x:c r="F220" t="inlineStr">
         <x:is>
@@ -7434,24 +7444,24 @@
     <x:row r="221">
       <x:c r="A221" t="inlineStr">
         <x:is>
-          <x:t>25/5981</x:t>
+          <x:t>25/5876</x:t>
         </x:is>
       </x:c>
       <x:c r="B221" t="inlineStr">
         <x:is>
-          <x:t>COMT0211</x:t>
+          <x:t>SANT0208</x:t>
         </x:is>
       </x:c>
       <x:c r="C221" t="inlineStr">
         <x:is>
-          <x:t>ACTIVIDADES AUXILIARES DE COMERCIO</x:t>
+          <x:t>TRANSPORTE SANITARIO</x:t>
         </x:is>
       </x:c>
       <x:c r="D221" s="1" t="n">
         <x:v>46089.9583333333</x:v>
       </x:c>
       <x:c r="E221" s="2" t="n">
-        <x:v>46223.9166666667</x:v>
+        <x:v>46294.9166666667</x:v>
       </x:c>
       <x:c r="F221" t="inlineStr">
         <x:is>
@@ -7460,31 +7470,31 @@
       </x:c>
       <x:c r="G221" t="inlineStr">
         <x:is>
-          <x:t>GRUPO CDM ESCUELAS PROFESIONALES S.L</x:t>
+          <x:t>CRUZ ROJA ESPAÑOLA</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="222">
       <x:c r="A222" t="inlineStr">
         <x:is>
-          <x:t>23/8438</x:t>
+          <x:t>25/5877</x:t>
         </x:is>
       </x:c>
       <x:c r="B222" t="inlineStr">
         <x:is>
-          <x:t>SEAG0209</x:t>
+          <x:t>SSCB0209</x:t>
         </x:is>
       </x:c>
       <x:c r="C222" t="inlineStr">
         <x:is>
-          <x:t>LIMPIEZA EN ESPACIOS ABIERTOS E INSTALACIONES INDUSTRIALES</x:t>
+          <x:t>DINAMIZACIÓN DE ACTIVIDADES DE TIEMPO LIBRE EDUCATIVO INFANTIL Y JUVENIL</x:t>
         </x:is>
       </x:c>
       <x:c r="D222" s="1" t="n">
-        <x:v>46086.9583333333</x:v>
+        <x:v>46089.9583333333</x:v>
       </x:c>
       <x:c r="E222" s="2" t="n">
-        <x:v>46128.9166666667</x:v>
+        <x:v>46233.9166666667</x:v>
       </x:c>
       <x:c r="F222" t="inlineStr">
         <x:is>
@@ -7493,31 +7503,31 @@
       </x:c>
       <x:c r="G222" t="inlineStr">
         <x:is>
-          <x:t>ARACOVE</x:t>
+          <x:t>CRUZ ROJA ESPAÑOLA</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="223">
       <x:c r="A223" t="inlineStr">
         <x:is>
-          <x:t>25/4949</x:t>
+          <x:t>25/5981</x:t>
         </x:is>
       </x:c>
       <x:c r="B223" t="inlineStr">
         <x:is>
-          <x:t>ADGD0110</x:t>
+          <x:t>COMT0211</x:t>
         </x:is>
       </x:c>
       <x:c r="C223" t="inlineStr">
         <x:is>
-          <x:t>ASISTENCIA EN LA GESTIÓN DE LOS PROCEDIMIENTOS TRIBUTARIOS</x:t>
+          <x:t>ACTIVIDADES AUXILIARES DE COMERCIO</x:t>
         </x:is>
       </x:c>
       <x:c r="D223" s="1" t="n">
-        <x:v>46086.9583333333</x:v>
+        <x:v>46089.9583333333</x:v>
       </x:c>
       <x:c r="E223" s="2" t="n">
-        <x:v>46231.9166666667</x:v>
+        <x:v>46223.9166666667</x:v>
       </x:c>
       <x:c r="F223" t="inlineStr">
         <x:is>
@@ -7526,42 +7536,47 @@
       </x:c>
       <x:c r="G223" t="inlineStr">
         <x:is>
-          <x:t>ANGEL FERNANDEZ-ROLDAN GONZALEZ</x:t>
+          <x:t>GRUPO CDM ESCUELAS PROFESIONALES S.L</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="224">
       <x:c r="A224" t="inlineStr">
         <x:is>
-          <x:t>25/5545</x:t>
+          <x:t>23/8438</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B224" t="inlineStr">
+        <x:is>
+          <x:t>SEAG0209</x:t>
         </x:is>
       </x:c>
       <x:c r="C224" t="inlineStr">
         <x:is>
-          <x:t>IMPLANTACIÓN Y ANIMACIÓN DE ESPACIOS COMERCIALES</x:t>
+          <x:t>LIMPIEZA EN ESPACIOS ABIERTOS E INSTALACIONES INDUSTRIALES</x:t>
         </x:is>
       </x:c>
       <x:c r="D224" s="1" t="n">
-        <x:v>46085.9583333333</x:v>
+        <x:v>46086.9583333333</x:v>
       </x:c>
       <x:c r="E224" s="2" t="n">
-        <x:v>46152.9166666667</x:v>
+        <x:v>46128.9166666667</x:v>
       </x:c>
       <x:c r="F224" t="inlineStr">
         <x:is>
-          <x:t>Teleformación</x:t>
+          <x:t>Presencial</x:t>
         </x:is>
       </x:c>
       <x:c r="G224" t="inlineStr">
         <x:is>
-          <x:t>CONECTANDO LOCAL, S.L.</x:t>
+          <x:t>ARACOVE</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="225">
       <x:c r="A225" t="inlineStr">
         <x:is>
-          <x:t>25/5604</x:t>
+          <x:t>25/4949</x:t>
         </x:is>
       </x:c>
       <x:c r="B225" t="inlineStr">
@@ -7575,19 +7590,19 @@
         </x:is>
       </x:c>
       <x:c r="D225" s="1" t="n">
-        <x:v>46085.9583333333</x:v>
+        <x:v>46086.9583333333</x:v>
       </x:c>
       <x:c r="E225" s="2" t="n">
-        <x:v>46280.9166666667</x:v>
+        <x:v>46231.9166666667</x:v>
       </x:c>
       <x:c r="F225" t="inlineStr">
         <x:is>
-          <x:t>Teleformación</x:t>
+          <x:t>Presencial</x:t>
         </x:is>
       </x:c>
       <x:c r="G225" t="inlineStr">
         <x:is>
-          <x:t>INSTITUTO DE FORMACION Y ESTUDIOS CAM, S.L.</x:t>
+          <x:t>ANGEL FERNANDEZ-ROLDAN GONZALEZ</x:t>
         </x:is>
       </x:c>
     </x:row>

--- a/public/madrid_cursos.xlsx
+++ b/public/madrid_cursos.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Buscador de Cursos - Público " sheetId="1" r:id="Rbccd04848d55481b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Buscador de Cursos - Público " sheetId="1" r:id="Rf0de38437a2b4ab2"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/public/madrid_cursos.xlsx
+++ b/public/madrid_cursos.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Buscador de Cursos - Público " sheetId="1" r:id="R6cc36a3728504f82"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Buscador de Cursos - Público " sheetId="1" r:id="Rbacb40c628984012"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/public/madrid_cursos.xlsx
+++ b/public/madrid_cursos.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Buscador de Cursos - Público " sheetId="1" r:id="R21492321083f4f6b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Buscador de Cursos - Público " sheetId="1" r:id="R02f11925f6d747b2"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/public/madrid_cursos.xlsx
+++ b/public/madrid_cursos.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Buscador de Cursos - Público " sheetId="1" r:id="R5330ae8ac3124bc5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Buscador de Cursos - Público " sheetId="1" r:id="R9cd3522bbad94d85"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/public/madrid_cursos.xlsx
+++ b/public/madrid_cursos.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Buscador de Cursos - Público " sheetId="1" r:id="R9cd3522bbad94d85"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Buscador de Cursos - Público " sheetId="1" r:id="Rf49ad596fdfe465e"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/public/madrid_cursos.xlsx
+++ b/public/madrid_cursos.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Buscador de Cursos - Público " sheetId="1" r:id="Rc4b2883a784c470d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Buscador de Cursos - Público " sheetId="1" r:id="R3d290786b74148a5"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/public/madrid_cursos.xlsx
+++ b/public/madrid_cursos.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Buscador de Cursos - Público " sheetId="1" r:id="Rb1da6b2f86fe466a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Buscador de Cursos - Público " sheetId="1" r:id="R3170a5cadc9b47cd"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/public/madrid_cursos.xlsx
+++ b/public/madrid_cursos.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Buscador de Cursos - Público " sheetId="1" r:id="R1aa40174359649f0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Buscador de Cursos - Público " sheetId="1" r:id="Raae72c4e5b8847cf"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/public/madrid_cursos.xlsx
+++ b/public/madrid_cursos.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Buscador de Cursos - Público " sheetId="1" r:id="R30c878108a2644fd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Buscador de Cursos - Público " sheetId="1" r:id="Rd8aa6c682f114f9b"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/public/madrid_cursos.xlsx
+++ b/public/madrid_cursos.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Buscador de Cursos - Público " sheetId="1" r:id="R855be799f027494e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Buscador de Cursos - Público " sheetId="1" r:id="R5f3a02da2b0c418b"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/public/madrid_cursos.xlsx
+++ b/public/madrid_cursos.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Buscador de Cursos - Público " sheetId="1" r:id="Rcc578491aaa64f47"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Buscador de Cursos - Público " sheetId="1" r:id="R6377d631927146b8"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/public/madrid_cursos.xlsx
+++ b/public/madrid_cursos.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Buscador de Cursos - Público " sheetId="1" r:id="R6377d631927146b8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Buscador de Cursos - Público " sheetId="1" r:id="Ra6e85978834d40f5"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/public/madrid_cursos.xlsx
+++ b/public/madrid_cursos.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Buscador de Cursos - Público " sheetId="1" r:id="R8b945e026a134d18"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Buscador de Cursos - Público " sheetId="1" r:id="R9805ed05375e48b5"/>
   </x:sheets>
 </x:workbook>
 </file>
